--- a/src/test/resources/TestCoverageDashboard_QA.xlsx
+++ b/src/test/resources/TestCoverageDashboard_QA.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB96F1D1-DF0B-422D-BCA8-C184DD3298BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696CB8ED-02C8-4055-BE8C-E74B01936500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCoverage" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -112,6 +112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -571,7 +572,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.90476190476190477</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1</c:v>
@@ -878,7 +879,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>9.5238095238095233E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2007,14 +2008,14 @@
   <dimension ref="A1:H42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="5.85546875" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="31.85546875"/>
+    <col min="2" max="2" customWidth="true" width="22.42578125"/>
+    <col min="3" max="3" customWidth="true" width="8.5703125"/>
+    <col min="4" max="4" customWidth="true" width="5.85546875"/>
+    <col min="5" max="5" customWidth="true" width="8.0"/>
+    <col min="6" max="6" customWidth="true" width="6.85546875"/>
+    <col min="7" max="7" customWidth="true" width="6.28515625"/>
+    <col min="8" max="8" customWidth="true" width="10.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -2051,83 +2052,83 @@
         <v>21</v>
       </c>
       <c r="C2" s="9">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D2" s="9">
         <v>0</v>
       </c>
       <c r="E2" s="9">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <f>IFERROR(C2/B2,0)</f>
-        <v>1</v>
-      </c>
-      <c r="G2" s="2">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="G2" s="2" t="n">
         <f>IFERROR(D2/B2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <f>IFERROR(E2/B2,0)</f>
-        <v>0</v>
+        <v>0.09523809523809523</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="9">
-        <v>4</v>
-      </c>
-      <c r="C3" s="9">
-        <v>4</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="B3" s="9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <f t="shared" ref="F3:F10" si="0">IFERROR(C3/B3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="G3" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G3" s="2" t="n">
         <f t="shared" ref="G3:G10" si="1">IFERROR(D3/B3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <f t="shared" ref="H3:H10" si="2">IFERROR(E3/B3,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="9">
-        <v>4</v>
-      </c>
-      <c r="C4" s="9">
-        <v>4</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="B4" s="9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G4" s="2" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="3" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2146,17 +2147,17 @@
       <c r="E5" s="9">
         <v>0</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="2" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="G5" s="2" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="3" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2175,17 +2176,17 @@
       <c r="E6" s="10">
         <v>0</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="5" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2204,108 +2205,108 @@
       <c r="E7" s="10">
         <v>0</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="5" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G7" s="5" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="9">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10">
-        <v>5</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="B8" s="9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="5" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G8" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="5" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="6" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="9">
-        <v>4</v>
-      </c>
-      <c r="C9" s="10">
-        <v>4</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="B9" s="9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="5" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G9" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="11" t="n">
         <f>SUM(B2:B9)</f>
-        <v>50</v>
-      </c>
-      <c r="C10" s="11">
+        <v>48.0</v>
+      </c>
+      <c r="C10" s="11" t="n">
         <f>SUM(C2:C9)</f>
-        <v>50</v>
-      </c>
-      <c r="D10" s="11">
+        <v>46.0</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <f>SUM(D2:D9)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="11">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <f>SUM(E2:E9)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="G10" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="8">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="8" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.041666666666666664</v>
       </c>
     </row>
     <row r="35" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
@@ -2405,12 +2406,12 @@
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.7109375"/>
+    <col min="2" max="2" customWidth="true" width="23.5703125"/>
+    <col min="5" max="5" customWidth="true" width="14.42578125"/>
+    <col min="6" max="6" customWidth="true" width="16.140625"/>
+    <col min="7" max="7" customWidth="true" width="15.140625"/>
+    <col min="8" max="8" customWidth="true" width="10.5703125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
@@ -2436,9 +2437,9 @@
       <c r="E3" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="13" t="n">
         <f>TestCoverage!B10</f>
-        <v>50</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -2448,9 +2449,9 @@
       <c r="E4" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="13" t="n">
         <f>TestCoverage!C10</f>
-        <v>50</v>
+        <v>46.0</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -2460,9 +2461,9 @@
       <c r="E5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="13" t="n">
         <f>TestCoverage!D10</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
@@ -2472,18 +2473,18 @@
       <c r="E6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="13" t="n">
         <f>TestCoverage!E10</f>
-        <v>0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="E7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="14" t="n">
         <f>TestCoverage!C10/TestCoverage!B10</f>
-        <v>1</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestCoverageDashboard_QA.xlsx
+++ b/src/test/resources/TestCoverageDashboard_QA.xlsx
@@ -3,22 +3,23 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{696CB8ED-02C8-4055-BE8C-E74B01936500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B209B6-2682-437E-A1E2-4FF04A0C24EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCoverage" sheetId="1" r:id="rId1"/>
     <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
+    <sheet name="Dashboard_Data" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>Functional Area</t>
   </si>
@@ -78,9 +79,6 @@
     <t xml:space="preserve">Overall Pass %:  </t>
   </si>
   <si>
-    <t>Test Coverage Dashboard</t>
-  </si>
-  <si>
     <t>Total Automated Tests</t>
   </si>
   <si>
@@ -107,13 +105,37 @@
   <si>
     <t>Timeline &amp; SLA Management</t>
   </si>
+  <si>
+    <t>Automation Execution Coverage - OneMAC SMART</t>
+  </si>
+  <si>
+    <t>Chart Label</t>
+  </si>
+  <si>
+    <t>Total Tests</t>
+  </si>
+  <si>
+    <t>Risk</t>
+  </si>
+  <si>
+    <t>API End To End</t>
+  </si>
+  <si>
+    <t>Execution Date:</t>
+  </si>
+  <si>
+    <t>Execution Date &amp; Time:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
+  </numFmts>
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,29 +150,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI Semibold"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Quire Sans Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -160,9 +161,56 @@
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,23 +225,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.749992370372631"/>
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -216,146 +277,90 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9E1F2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E1F2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E1F2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E1F2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFFF"/>
+      <color rgb="FFF7F7F7"/>
+      <color rgb="FF4F81BD"/>
+      <color rgb="FF1F4E79"/>
+      <color rgb="FFDCE6F1"/>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFFF694B"/>
+      <color rgb="FFFF9D89"/>
+      <color rgb="FFFF5C3B"/>
       <color rgb="FFFF5050"/>
-      <color rgb="FFFFFF66"/>
-      <color rgb="FFFF5C3B"/>
     </mruColors>
   </colors>
   <extLst>
@@ -397,9 +402,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
@@ -407,6 +412,8 @@
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:rPr>
               <a:t>Execution Status by Functional Area</a:t>
             </a:r>
@@ -433,9 +440,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -446,15 +453,15 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="percentStacked"/>
+        <c:barDir val="bar"/>
+        <c:grouping val="stacked"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="4"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>TestCoverage!$F$1</c:f>
+              <c:f>Dashboard_Data!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -468,6 +475,7 @@
               <a:schemeClr val="accent6">
                 <a:lumMod val="40000"/>
                 <a:lumOff val="60000"/>
+                <a:alpha val="98000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -477,159 +485,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>TestCoverage!$A$2:$A$9</c:f>
-              <c:strCache>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>Validations &amp; Business Rules</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>RAI Management</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>SRT Review Workflow</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Workflow &amp; Status Transitions</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Record Lifecycle Management</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>User Access &amp; Permissions</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Assignment &amp; Routing</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Timeline &amp; SLA Management</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>TestCoverage!$F$2:$F$9</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>0.90476190476190477</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FB6E-45FE-8991-B3D9A8DE49D8}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="5"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>TestCoverage!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Fail %</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="FF5050"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="[&lt;1]0%;;" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -689,64 +545,70 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestCoverage!$A$2:$A$9</c:f>
+              <c:f>Dashboard_Data!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Validations &amp; Business Rules</c:v>
+                  <c:v>Validations &amp; Business Rules (33)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>RAI Management</c:v>
+                  <c:v>SRT Review Workflow ()</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>SRT Review Workflow</c:v>
+                  <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Workflow &amp; Status Transitions</c:v>
+                  <c:v>RAI Management ()</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Record Lifecycle Management</c:v>
+                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>User Access &amp; Permissions</c:v>
+                  <c:v>Record Lifecycle Management (11)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Assignment &amp; Routing</c:v>
+                  <c:v>User Access &amp; Permissions (1)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Timeline &amp; SLA Management</c:v>
+                  <c:v>API End To End ()</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Assignment &amp; Routing ()</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestCoverage!$G$2:$G$9</c:f>
+              <c:f>Dashboard_Data!$B$2:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.93939393939393945</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -754,27 +616,27 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FB6E-45FE-8991-B3D9A8DE49D8}"/>
+              <c16:uniqueId val="{00000000-FB6E-45FE-8991-B3D9A8DE49D8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:ser>
-          <c:idx val="6"/>
-          <c:order val="2"/>
+          <c:idx val="5"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>TestCoverage!$H$1</c:f>
+              <c:f>Dashboard_Data!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Blocked %</c:v>
+                  <c:v>Fail %</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="FFC000"/>
+              <a:srgbClr val="FF694B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -783,7 +645,7 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
+            <c:numFmt formatCode="[&gt;0]0%;;" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -813,6 +675,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -842,44 +705,47 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>TestCoverage!$A$2:$A$9</c:f>
+              <c:f>Dashboard_Data!$A$2:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>Validations &amp; Business Rules</c:v>
+                  <c:v>Validations &amp; Business Rules (33)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>RAI Management</c:v>
+                  <c:v>SRT Review Workflow ()</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>SRT Review Workflow</c:v>
+                  <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Workflow &amp; Status Transitions</c:v>
+                  <c:v>RAI Management ()</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Record Lifecycle Management</c:v>
+                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>User Access &amp; Permissions</c:v>
+                  <c:v>Record Lifecycle Management (11)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Assignment &amp; Routing</c:v>
+                  <c:v>User Access &amp; Permissions (1)</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Timeline &amp; SLA Management</c:v>
+                  <c:v>API End To End ()</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Assignment &amp; Routing ()</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>TestCoverage!$H$2:$H$9</c:f>
+              <c:f>Dashboard_Data!$C$2:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>9.5238095238095233E-2</c:v>
+                  <c:v>6.0606060606060608E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -900,6 +766,169 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FB6E-45FE-8991-B3D9A8DE49D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard_Data!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Blocked %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="[&gt;0]0%;;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard_Data!$A$2:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>Validations &amp; Business Rules (33)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SRT Review Workflow ()</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Timeline &amp; SLA Management (10)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>RAI Management ()</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Record Lifecycle Management (11)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>User Access &amp; Permissions (1)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>API End To End ()</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Assignment &amp; Routing ()</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard_Data!$D$2:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -912,14 +941,15 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="150"/>
+        <c:gapWidth val="286"/>
         <c:overlap val="100"/>
         <c:axId val="974676704"/>
         <c:axId val="974680544"/>
@@ -927,10 +957,10 @@
       <c:catAx>
         <c:axId val="974676704"/>
         <c:scaling>
-          <c:orientation val="minMax"/>
+          <c:orientation val="maxMin"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -949,7 +979,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="t" anchorCtr="0"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
@@ -960,7 +990,7 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
@@ -979,13 +1009,15 @@
         <c:axId val="974680544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
+        <c:axPos val="t"/>
         <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+        <c:tickLblPos val="high"/>
         <c:spPr>
           <a:noFill/>
           <a:ln>
@@ -1649,16 +1681,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>726281</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>209000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>148828</xdr:rowOff>
+      <xdr:rowOff>144432</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>246289</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>186929</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>227134</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>87924</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2005,362 +2037,295 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7427542-4B70-47E8-B3EC-391C17B60C17}">
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="31.85546875"/>
-    <col min="2" max="2" customWidth="true" width="22.42578125"/>
-    <col min="3" max="3" customWidth="true" width="8.5703125"/>
-    <col min="4" max="4" customWidth="true" width="5.85546875"/>
-    <col min="5" max="5" customWidth="true" width="8.0"/>
-    <col min="6" max="6" customWidth="true" width="6.85546875"/>
-    <col min="7" max="7" customWidth="true" width="6.28515625"/>
-    <col min="8" max="8" customWidth="true" width="10.140625"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
+    <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="21">
+        <v>46093.462851273151</v>
+      </c>
+      <c r="D1" s="22"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="17">
+        <v>33</v>
+      </c>
+      <c r="C3" s="17">
+        <v>31</v>
+      </c>
+      <c r="D3" s="17">
+        <v>2</v>
+      </c>
+      <c r="E3" s="17">
+        <v>0</v>
+      </c>
+      <c r="F3" s="13">
+        <f>IFERROR(C3/B3,0)</f>
+        <v>0.93939393939393945</v>
+      </c>
+      <c r="G3" s="13">
+        <f>IFERROR(D3/B3,0)</f>
+        <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="H3" s="13">
+        <f>IFERROR(E3/B3,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18">
+        <v>3</v>
+      </c>
+      <c r="C6" s="18">
+        <v>3</v>
+      </c>
+      <c r="D6" s="18">
+        <v>0</v>
+      </c>
+      <c r="E6" s="18">
+        <v>0</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" ref="F6:F12" si="0">IFERROR(C6/B6,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" ref="G6:G12" si="1">IFERROR(D6/B6,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" ref="H6:H12" si="2">IFERROR(E6/B6,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="17">
+        <v>11</v>
+      </c>
+      <c r="C7" s="17">
+        <v>11</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G7" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="B8" s="18">
         <v>1</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="C8" s="18">
+        <v>1</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0</v>
+      </c>
+      <c r="E8" s="18">
+        <v>0</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="17">
+        <v>10</v>
+      </c>
+      <c r="C11" s="17">
+        <v>10</v>
+      </c>
+      <c r="D11" s="17">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="19">
+        <f>SUM(B3:B11)</f>
+        <v>58</v>
+      </c>
+      <c r="C12" s="19">
+        <f>SUM(C3:C11)</f>
+        <v>56</v>
+      </c>
+      <c r="D12" s="19">
+        <f>SUM(D3:D11)</f>
         <v>2</v>
       </c>
-      <c r="E1" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="9">
-        <v>21</v>
-      </c>
-      <c r="C2" s="9">
-        <v>19</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0</v>
-      </c>
-      <c r="E2" s="9">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <f>IFERROR(C2/B2,0)</f>
-        <v>0.9047619047619048</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <f>IFERROR(D2/B2,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <f>IFERROR(E2/B2,0)</f>
-        <v>0.09523809523809523</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <f t="shared" ref="F3:F10" si="0">IFERROR(C3/B3,0)</f>
-        <v>1.0</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <f t="shared" ref="G3:G10" si="1">IFERROR(D3/B3,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <f t="shared" ref="H3:H10" si="2">IFERROR(E3/B3,0)</f>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C4" s="9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="2" t="n">
+      <c r="E12" s="19">
+        <f>SUM(E3:E11)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G4" s="2" t="n">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="G12" s="5">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="3" t="n">
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="H12" s="5">
         <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="9">
-        <v>3</v>
-      </c>
-      <c r="C5" s="9">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="9">
-        <v>6</v>
-      </c>
-      <c r="C6" s="10">
-        <v>6</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="9">
-        <v>3</v>
-      </c>
-      <c r="C7" s="10">
-        <v>3</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="9" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <f t="shared" si="2"/>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="11" t="n">
-        <f>SUM(B2:B9)</f>
-        <v>48.0</v>
-      </c>
-      <c r="C10" s="11" t="n">
-        <f>SUM(C2:C9)</f>
-        <v>46.0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <f>SUM(D2:D9)</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <f>SUM(E2:E9)</f>
-        <v>2.0</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <f t="shared" si="0"/>
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <f t="shared" si="2"/>
-        <v>0.041666666666666664</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B35" s="17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B38" s="17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B39" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B40" s="17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="B42" s="17" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:H1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="between">
-      <formula>0.5</formula>
-      <formula>0.79</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThanOrEqual">
-      <formula>0.8</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F10">
+  <conditionalFormatting sqref="F3:F12">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2372,7 +2337,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G10">
+  <conditionalFormatting sqref="G3:G12">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2384,7 +2349,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H10">
+  <conditionalFormatting sqref="H3:H12">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2406,86 +2371,143 @@
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="14.7109375"/>
-    <col min="2" max="2" customWidth="true" width="23.5703125"/>
-    <col min="5" max="5" customWidth="true" width="14.42578125"/>
-    <col min="6" max="6" customWidth="true" width="16.140625"/>
-    <col min="7" max="7" customWidth="true" width="15.140625"/>
-    <col min="8" max="8" customWidth="true" width="10.5703125"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="A1" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="E3" s="16" t="s">
+    <row r="1" spans="1:12" ht="37.5" x14ac:dyDescent="0.7">
+      <c r="A1" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="10">
+        <f>TestCoverage!C1</f>
+        <v>46093.462851273151</v>
+      </c>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="13" t="n">
-        <f>TestCoverage!B10</f>
-        <v>48.0</v>
-      </c>
+      <c r="F3" s="25">
+        <f>TestCoverage!B12</f>
+        <v>58</v>
+      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="E4" s="15" t="s">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="13" t="n">
-        <f>TestCoverage!C10</f>
-        <v>46.0</v>
-      </c>
+      <c r="F4" s="25">
+        <f>TestCoverage!C12</f>
+        <v>56</v>
+      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="E5" s="15" t="s">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="13" t="n">
-        <f>TestCoverage!D10</f>
-        <v>0.0</v>
-      </c>
+      <c r="F5" s="25">
+        <f>TestCoverage!D12</f>
+        <v>2</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="E6" s="15" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <f>TestCoverage!E10</f>
-        <v>2.0</v>
-      </c>
+      <c r="F6" s="25">
+        <f>TestCoverage!E12</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="E7" s="15" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="14" t="n">
-        <f>TestCoverage!C10/TestCoverage!B10</f>
-        <v>0.9583333333333334</v>
-      </c>
+      <c r="F7" s="26">
+        <f>TestCoverage!C12/TestCoverage!B12</f>
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2495,4 +2517,299 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC817E08-797F-444D-BF6E-D4C8FC527215}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="4" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <f>TestCoverage!A3 &amp; " (" &amp; TestCoverage!B3 &amp; ")"</f>
+        <v>Validations &amp; Business Rules (33)</v>
+      </c>
+      <c r="B2" s="3">
+        <f>TestCoverage!F3</f>
+        <v>0.93939393939393945</v>
+      </c>
+      <c r="C2" s="3">
+        <f>TestCoverage!G3</f>
+        <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="D2" s="3">
+        <f>TestCoverage!H3</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <f t="shared" ref="E2:E8" si="0">C2 + D2</f>
+        <v>6.0606060606060608E-2</v>
+      </c>
+      <c r="F2">
+        <f>TestCoverage!B3</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <f>TestCoverage!A5 &amp; " (" &amp; TestCoverage!B5 &amp; ")"</f>
+        <v>SRT Review Workflow ()</v>
+      </c>
+      <c r="B3" s="3">
+        <f>TestCoverage!F5</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <f>TestCoverage!G5</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <f>TestCoverage!H5</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>TestCoverage!B5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <f>TestCoverage!A11 &amp; " (" &amp; TestCoverage!B11 &amp; ")"</f>
+        <v>Timeline &amp; SLA Management (10)</v>
+      </c>
+      <c r="B4" s="3">
+        <f>TestCoverage!F11</f>
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <f>TestCoverage!G11</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <f>TestCoverage!H11</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>TestCoverage!B11</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <f>TestCoverage!A4 &amp; " (" &amp; TestCoverage!B4 &amp; ")"</f>
+        <v>RAI Management ()</v>
+      </c>
+      <c r="B5" s="3">
+        <f>TestCoverage!F4</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <f>TestCoverage!G4</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <f>TestCoverage!H4</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>TestCoverage!B4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f>TestCoverage!A6 &amp; " (" &amp; TestCoverage!B6 &amp; ")"</f>
+        <v>Workflow &amp; Status Transitions (3)</v>
+      </c>
+      <c r="B6" s="3">
+        <f>TestCoverage!F6</f>
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <f>TestCoverage!G6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <f>TestCoverage!H6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>TestCoverage!B6</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <f>TestCoverage!A7 &amp; " (" &amp; TestCoverage!B7 &amp; ")"</f>
+        <v>Record Lifecycle Management (11)</v>
+      </c>
+      <c r="B7" s="3">
+        <f>TestCoverage!F7</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <f>TestCoverage!G7</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <f>TestCoverage!H7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>TestCoverage!B7</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <f>TestCoverage!A8 &amp; " (" &amp; TestCoverage!B8 &amp; ")"</f>
+        <v>User Access &amp; Permissions (1)</v>
+      </c>
+      <c r="B8" s="3">
+        <f>TestCoverage!F8</f>
+        <v>1</v>
+      </c>
+      <c r="C8" s="3">
+        <f>TestCoverage!G8</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <f>TestCoverage!H8</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>TestCoverage!B8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <f>TestCoverage!A10 &amp; " (" &amp; TestCoverage!B10 &amp; ")"</f>
+        <v>API End To End ()</v>
+      </c>
+      <c r="B9" s="3">
+        <f>TestCoverage!F10</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <f>TestCoverage!G10</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <f>TestCoverage!H10</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <f>C10 + D10</f>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f>TestCoverage!B10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <f>TestCoverage!A9 &amp; " (" &amp; TestCoverage!B9 &amp; ")"</f>
+        <v>Assignment &amp; Routing ()</v>
+      </c>
+      <c r="B10" s="3">
+        <f>TestCoverage!F9</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <f>TestCoverage!G9</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <f>TestCoverage!H9</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <f>C9 + D9</f>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f>TestCoverage!B9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <f>TestCoverage!A12 &amp; " (" &amp; TestCoverage!B12 &amp; ")"</f>
+        <v>TOTAL (58)</v>
+      </c>
+      <c r="B11" s="3">
+        <f>TestCoverage!F12</f>
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="C11" s="3">
+        <f>TestCoverage!G12</f>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="D11" s="3">
+        <f>TestCoverage!H12</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="3"/>
+      <c r="F11">
+        <f>TestCoverage!B12</f>
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F11">
+    <sortCondition descending="1" ref="E2:E11"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/TestCoverageDashboard_QA.xlsx
+++ b/src/test/resources/TestCoverageDashboard_QA.xlsx
@@ -5,18 +5,21 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B209B6-2682-437E-A1E2-4FF04A0C24EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB125AE9-DB5A-430F-A1BB-F3D1FF852B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCoverage" sheetId="1" r:id="rId1"/>
     <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
-    <sheet name="Dashboard_Data" sheetId="3" r:id="rId3"/>
+    <sheet name="Dashboard_Data" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dashboard_Data!$A$1:$F$16</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>Functional Area</t>
   </si>
@@ -125,6 +128,21 @@
   </si>
   <si>
     <t>Execution Date &amp; Time:</t>
+  </si>
+  <si>
+    <t>Search &amp; Filters</t>
+  </si>
+  <si>
+    <t>Reporting &amp; Data Export</t>
+  </si>
+  <si>
+    <t>Accessibility (Section 508 Compliance)</t>
+  </si>
+  <si>
+    <t>Email Notifications &amp; Alerts</t>
+  </si>
+  <si>
+    <t>Document Management</t>
   </si>
 </sst>
 </file>
@@ -135,7 +153,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,19 +196,6 @@
     </font>
     <font>
       <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Segoe UI"/>
@@ -204,13 +209,14 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F4E79"/>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,8 +259,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -277,11 +289,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -297,9 +318,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -309,10 +328,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -324,23 +340,21 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -485,116 +499,75 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:numFmt formatCode="[&lt;1]0%;;" sourceLinked="0"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard_Data!$A$2:$A$10</c:f>
+              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
+                  <c:v>RAI Management (4)</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Validations &amp; Business Rules (33)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>SRT Review Workflow ()</c:v>
-                </c:pt>
                 <c:pt idx="2">
+                  <c:v>SRT Review Workflow (5)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Record Lifecycle Management (11)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>User Access &amp; Permissions (1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Assignment &amp; Routing (4)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>API End To End (4)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Search &amp; Filters (5)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Reporting &amp; Data Export (3)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Accessibility (Section 508 Compliance) (4)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Email Notifications &amp; Alerts (3)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>RAI Management ()</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Record Lifecycle Management (11)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>API End To End ()</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Assignment &amp; Routing ()</c:v>
+                <c:pt idx="13">
+                  <c:v>Document Management ()</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard_Data!$B$2:$B$10</c:f>
+              <c:f>Dashboard_Data!$B$2:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>0.93939393939393945</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -606,9 +579,24 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.3333333333333333</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -645,110 +633,69 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:numFmt formatCode="[&gt;0]0%;;" sourceLinked="0"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard_Data!$A$2:$A$10</c:f>
+              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
+                  <c:v>RAI Management (4)</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Validations &amp; Business Rules (33)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>SRT Review Workflow ()</c:v>
-                </c:pt>
                 <c:pt idx="2">
+                  <c:v>SRT Review Workflow (5)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Record Lifecycle Management (11)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>User Access &amp; Permissions (1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Assignment &amp; Routing (4)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>API End To End (4)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Search &amp; Filters (5)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Reporting &amp; Data Export (3)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Accessibility (Section 508 Compliance) (4)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Email Notifications &amp; Alerts (3)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>RAI Management ()</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Record Lifecycle Management (11)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>API End To End ()</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Assignment &amp; Routing ()</c:v>
+                <c:pt idx="13">
+                  <c:v>Document Management ()</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard_Data!$C$2:$C$10</c:f>
+              <c:f>Dashboard_Data!$C$2:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>6.0606060606060608E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -769,6 +716,21 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -805,107 +767,66 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:numFmt formatCode="[&gt;0]0%;;" sourceLinked="0"/>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="ctr"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
+            <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard_Data!$A$2:$A$10</c:f>
+              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
               <c:strCache>
-                <c:ptCount val="9"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
+                  <c:v>RAI Management (4)</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Validations &amp; Business Rules (33)</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>SRT Review Workflow ()</c:v>
-                </c:pt>
                 <c:pt idx="2">
+                  <c:v>SRT Review Workflow (5)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Record Lifecycle Management (11)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>User Access &amp; Permissions (1)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Assignment &amp; Routing (4)</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>API End To End (4)</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Search &amp; Filters (5)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Reporting &amp; Data Export (3)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Accessibility (Section 508 Compliance) (4)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Email Notifications &amp; Alerts (3)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>RAI Management ()</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Record Lifecycle Management (11)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>API End To End ()</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Assignment &amp; Routing ()</c:v>
+                <c:pt idx="13">
+                  <c:v>Document Management ()</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Dashboard_Data!$D$2:$D$10</c:f>
+              <c:f>Dashboard_Data!$D$2:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -929,6 +850,21 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -949,7 +885,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="286"/>
+        <c:gapWidth val="30"/>
         <c:overlap val="100"/>
         <c:axId val="974676704"/>
         <c:axId val="974680544"/>
@@ -1059,6 +995,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.46588824688972519"/>
+          <c:y val="0.9143754541065745"/>
+          <c:w val="0.17214009171974623"/>
+          <c:h val="7.9481106747818109E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2037,13 +1983,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7427542-4B70-47E8-B3EC-391C17B60C17}">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.85546875" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="6.85546875" customWidth="1"/>
     <col min="7" max="7" width="6.28515625" customWidth="1"/>
@@ -2051,281 +1997,489 @@
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="21">
-        <v>46093.462851273151</v>
-      </c>
+      <c r="B1" s="22">
+        <v>46094.503644780096</v>
+      </c>
+      <c r="C1" s="22"/>
       <c r="D1" s="22"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="17" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="14">
         <v>33</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="14">
         <v>31</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="14">
         <v>2</v>
       </c>
-      <c r="E3" s="17">
-        <v>0</v>
-      </c>
-      <c r="F3" s="13">
+      <c r="E3" s="14">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11">
         <f>IFERROR(C3/B3,0)</f>
         <v>0.93939393939393945</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="11">
         <f>IFERROR(D3/B3,0)</f>
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="11">
         <f>IFERROR(E3/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
+      <c r="B4" s="15">
+        <v>4</v>
+      </c>
+      <c r="C4" s="15">
+        <v>2</v>
+      </c>
+      <c r="D4" s="15">
+        <v>0</v>
+      </c>
+      <c r="E4" s="15">
+        <v>2</v>
+      </c>
+      <c r="F4" s="11">
+        <f t="shared" ref="F4:F16" si="0">IFERROR(C4/B4,0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="11">
+        <f t="shared" ref="G4:G14" si="1">IFERROR(D4/B4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="11">
+        <f t="shared" ref="H4:H14" si="2">IFERROR(E4/B4,0)</f>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="18">
-        <v>3</v>
-      </c>
-      <c r="C6" s="18">
-        <v>3</v>
-      </c>
-      <c r="D6" s="18">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15">
-        <f t="shared" ref="F6:F12" si="0">IFERROR(C6/B6,0)</f>
-        <v>1</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" ref="G6:G12" si="1">IFERROR(D6/B6,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="15">
-        <f t="shared" ref="H6:H12" si="2">IFERROR(E6/B6,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="17">
-        <v>11</v>
-      </c>
-      <c r="C7" s="17">
-        <v>11</v>
-      </c>
-      <c r="D7" s="17">
-        <v>0</v>
-      </c>
-      <c r="E7" s="17">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13">
+      <c r="B5" s="14">
+        <v>5</v>
+      </c>
+      <c r="C5" s="14">
+        <v>5</v>
+      </c>
+      <c r="D5" s="14">
+        <v>0</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0</v>
+      </c>
+      <c r="F5" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G5" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H5" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="18">
-        <v>1</v>
-      </c>
-      <c r="C8" s="18">
-        <v>1</v>
-      </c>
-      <c r="D8" s="18">
-        <v>0</v>
-      </c>
-      <c r="E8" s="18">
-        <v>0</v>
-      </c>
-      <c r="F8" s="15">
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="15">
+        <v>3</v>
+      </c>
+      <c r="C6" s="15">
+        <v>3</v>
+      </c>
+      <c r="D6" s="15">
+        <v>0</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0</v>
+      </c>
+      <c r="F6" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G6" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H6" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="17">
-        <v>10</v>
-      </c>
-      <c r="C11" s="17">
-        <v>10</v>
-      </c>
-      <c r="D11" s="17">
-        <v>0</v>
-      </c>
-      <c r="E11" s="17">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="14">
+        <v>11</v>
+      </c>
+      <c r="C7" s="14">
+        <v>11</v>
+      </c>
+      <c r="D7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G7" s="11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H7" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="15">
+        <v>1</v>
+      </c>
+      <c r="C8" s="15">
+        <v>1</v>
+      </c>
+      <c r="D8" s="15">
+        <v>0</v>
+      </c>
+      <c r="E8" s="15">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="14">
+        <v>4</v>
+      </c>
+      <c r="C9" s="14">
+        <v>4</v>
+      </c>
+      <c r="D9" s="14">
+        <v>0</v>
+      </c>
+      <c r="E9" s="14">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="15">
+        <v>4</v>
+      </c>
+      <c r="C10" s="15">
+        <v>4</v>
+      </c>
+      <c r="D10" s="15">
+        <v>0</v>
+      </c>
+      <c r="E10" s="15">
+        <v>0</v>
+      </c>
+      <c r="F10" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="14">
+        <v>5</v>
+      </c>
+      <c r="C11" s="14">
+        <v>5</v>
+      </c>
+      <c r="D11" s="14">
+        <v>0</v>
+      </c>
+      <c r="E11" s="14">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="15">
+        <v>3</v>
+      </c>
+      <c r="C12" s="15">
+        <v>4</v>
+      </c>
+      <c r="D12" s="15">
+        <v>0</v>
+      </c>
+      <c r="E12" s="15">
+        <v>0</v>
+      </c>
+      <c r="F12" s="11">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="14">
+        <v>4</v>
+      </c>
+      <c r="C13" s="14">
+        <v>4</v>
+      </c>
+      <c r="D13" s="14">
+        <v>0</v>
+      </c>
+      <c r="E13" s="14">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="15">
+        <v>3</v>
+      </c>
+      <c r="C14" s="15">
+        <v>4</v>
+      </c>
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11">
+        <f t="shared" si="0"/>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="G14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="14">
+        <v>10</v>
+      </c>
+      <c r="C15" s="14">
+        <v>10</v>
+      </c>
+      <c r="D15" s="14">
+        <v>0</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G15" s="11">
+        <f>IFERROR(D15/B15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="11">
+        <f t="shared" ref="H15:H17" si="3">IFERROR(E15/B15,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G16" s="11">
+        <f>IFERROR(D16/B16,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="11">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="19">
-        <f>SUM(B3:B11)</f>
-        <v>58</v>
-      </c>
-      <c r="C12" s="19">
-        <f>SUM(C3:C11)</f>
-        <v>56</v>
-      </c>
-      <c r="D12" s="19">
-        <f>SUM(D3:D11)</f>
+      <c r="B17" s="16">
+        <f>SUM(B3:B15)</f>
+        <v>90</v>
+      </c>
+      <c r="C17" s="16">
+        <f>SUM(C3:C15)</f>
+        <v>88</v>
+      </c>
+      <c r="D17" s="16">
+        <f>SUM(D3:D15)</f>
         <v>2</v>
       </c>
-      <c r="E12" s="19">
-        <f>SUM(E3:E11)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="5">
-        <f t="shared" si="0"/>
-        <v>0.96551724137931039</v>
-      </c>
-      <c r="G12" s="5">
-        <f t="shared" si="1"/>
-        <v>3.4482758620689655E-2</v>
-      </c>
-      <c r="H12" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="E17" s="16">
+        <f>SUM(E3:E15)</f>
+        <v>2</v>
+      </c>
+      <c r="F17" s="5">
+        <f t="shared" ref="F17" si="4">IFERROR(C17/B17,0)</f>
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" ref="G17" si="5">IFERROR(D17/B17,0)</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="H17" s="5">
+        <f t="shared" si="3"/>
+        <v>2.2222222222222223E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:H1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F3:F12">
+  <conditionalFormatting sqref="F3:F17">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2337,7 +2491,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G12">
+  <conditionalFormatting sqref="G3:G17">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2349,7 +2503,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H12">
+  <conditionalFormatting sqref="H3:H17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -2379,33 +2533,33 @@
     <col min="8" max="8" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="37.5" x14ac:dyDescent="0.7">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:12" ht="30.75" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="10">
-        <f>TestCoverage!C1</f>
-        <v>46093.462851273151</v>
+      <c r="F2" s="9">
+        <f>TestCoverage!B1</f>
+        <v>46094.503644780096</v>
       </c>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -2419,12 +2573,12 @@
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="6"/>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="25">
-        <f>TestCoverage!B12</f>
-        <v>58</v>
+      <c r="F3" s="19">
+        <f>TestCoverage!B17</f>
+        <v>90</v>
       </c>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -2438,12 +2592,12 @@
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="6"/>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="25">
-        <f>TestCoverage!C12</f>
-        <v>56</v>
+      <c r="F4" s="19">
+        <f>TestCoverage!C17</f>
+        <v>88</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -2457,11 +2611,11 @@
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="25">
-        <f>TestCoverage!D12</f>
+      <c r="F5" s="19">
+        <f>TestCoverage!D17</f>
         <v>2</v>
       </c>
       <c r="G5" s="6"/>
@@ -2476,12 +2630,12 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="25">
-        <f>TestCoverage!E12</f>
-        <v>0</v>
+      <c r="F6" s="19">
+        <f>TestCoverage!E17</f>
+        <v>2</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -2495,12 +2649,12 @@
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="26">
-        <f>TestCoverage!C12/TestCoverage!B12</f>
-        <v>0.96551724137931039</v>
+      <c r="F7" s="21">
+        <f>TestCoverage!C17/TestCoverage!B17</f>
+        <v>0.97777777777777775</v>
       </c>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
@@ -2521,10 +2675,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC817E08-797F-444D-BF6E-D4C8FC527215}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
     <col min="4" max="5" width="13.85546875" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" customWidth="1"/>
   </cols>
@@ -2551,71 +2706,71 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
+        <f>TestCoverage!A4 &amp; " (" &amp; TestCoverage!B4 &amp; ")"</f>
+        <v>RAI Management (4)</v>
+      </c>
+      <c r="B2" s="3">
+        <f>TestCoverage!F4</f>
+        <v>0.5</v>
+      </c>
+      <c r="C2" s="3">
+        <f>TestCoverage!G4</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <f>TestCoverage!H4</f>
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="3">
+        <f t="shared" ref="E2:E15" si="0">C2 + D2</f>
+        <v>0.5</v>
+      </c>
+      <c r="F2">
+        <f>TestCoverage!B4</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
         <f>TestCoverage!A3 &amp; " (" &amp; TestCoverage!B3 &amp; ")"</f>
         <v>Validations &amp; Business Rules (33)</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B3" s="3">
         <f>TestCoverage!F3</f>
         <v>0.93939393939393945</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C3" s="3">
         <f>TestCoverage!G3</f>
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D3" s="3">
         <f>TestCoverage!H3</f>
         <v>0</v>
       </c>
-      <c r="E2" s="3">
-        <f t="shared" ref="E2:E8" si="0">C2 + D2</f>
+      <c r="E3" s="3">
+        <f t="shared" si="0"/>
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="F2">
+      <c r="F3">
         <f>TestCoverage!B3</f>
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <f>TestCoverage!A5 &amp; " (" &amp; TestCoverage!B5 &amp; ")"</f>
-        <v>SRT Review Workflow ()</v>
-      </c>
-      <c r="B3" s="3">
-        <f>TestCoverage!F5</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <f>TestCoverage!G5</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <f>TestCoverage!H5</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <f>TestCoverage!B5</f>
-        <v>0</v>
-      </c>
-    </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <f>TestCoverage!A11 &amp; " (" &amp; TestCoverage!B11 &amp; ")"</f>
-        <v>Timeline &amp; SLA Management (10)</v>
+        <f>TestCoverage!A5 &amp; " (" &amp; TestCoverage!B5 &amp; ")"</f>
+        <v>SRT Review Workflow (5)</v>
       </c>
       <c r="B4" s="3">
-        <f>TestCoverage!F11</f>
+        <f>TestCoverage!F5</f>
         <v>1</v>
       </c>
       <c r="C4" s="3">
-        <f>TestCoverage!G11</f>
+        <f>TestCoverage!G5</f>
         <v>0</v>
       </c>
       <c r="D4" s="3">
-        <f>TestCoverage!H11</f>
+        <f>TestCoverage!H5</f>
         <v>0</v>
       </c>
       <c r="E4" s="3">
@@ -2623,25 +2778,25 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <f>TestCoverage!B11</f>
-        <v>10</v>
+        <f>TestCoverage!B5</f>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <f>TestCoverage!A4 &amp; " (" &amp; TestCoverage!B4 &amp; ")"</f>
-        <v>RAI Management ()</v>
+        <f>TestCoverage!A6 &amp; " (" &amp; TestCoverage!B6 &amp; ")"</f>
+        <v>Workflow &amp; Status Transitions (3)</v>
       </c>
       <c r="B5" s="3">
-        <f>TestCoverage!F4</f>
-        <v>0</v>
+        <f>TestCoverage!F6</f>
+        <v>1</v>
       </c>
       <c r="C5" s="3">
-        <f>TestCoverage!G4</f>
+        <f>TestCoverage!G6</f>
         <v>0</v>
       </c>
       <c r="D5" s="3">
-        <f>TestCoverage!H4</f>
+        <f>TestCoverage!H6</f>
         <v>0</v>
       </c>
       <c r="E5" s="3">
@@ -2649,25 +2804,25 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <f>TestCoverage!B4</f>
-        <v>0</v>
+        <f>TestCoverage!B6</f>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <f>TestCoverage!A6 &amp; " (" &amp; TestCoverage!B6 &amp; ")"</f>
-        <v>Workflow &amp; Status Transitions (3)</v>
+        <f>TestCoverage!A7 &amp; " (" &amp; TestCoverage!B7 &amp; ")"</f>
+        <v>Record Lifecycle Management (11)</v>
       </c>
       <c r="B6" s="3">
-        <f>TestCoverage!F6</f>
+        <f>TestCoverage!F7</f>
         <v>1</v>
       </c>
       <c r="C6" s="3">
-        <f>TestCoverage!G6</f>
+        <f>TestCoverage!G7</f>
         <v>0</v>
       </c>
       <c r="D6" s="3">
-        <f>TestCoverage!H6</f>
+        <f>TestCoverage!H7</f>
         <v>0</v>
       </c>
       <c r="E6" s="3">
@@ -2675,25 +2830,25 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <f>TestCoverage!B6</f>
-        <v>3</v>
+        <f>TestCoverage!B7</f>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <f>TestCoverage!A7 &amp; " (" &amp; TestCoverage!B7 &amp; ")"</f>
-        <v>Record Lifecycle Management (11)</v>
+        <f>TestCoverage!A8 &amp; " (" &amp; TestCoverage!B8 &amp; ")"</f>
+        <v>User Access &amp; Permissions (1)</v>
       </c>
       <c r="B7" s="3">
-        <f>TestCoverage!F7</f>
+        <f>TestCoverage!F8</f>
         <v>1</v>
       </c>
       <c r="C7" s="3">
-        <f>TestCoverage!G7</f>
+        <f>TestCoverage!G8</f>
         <v>0</v>
       </c>
       <c r="D7" s="3">
-        <f>TestCoverage!H7</f>
+        <f>TestCoverage!H8</f>
         <v>0</v>
       </c>
       <c r="E7" s="3">
@@ -2701,25 +2856,25 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <f>TestCoverage!B7</f>
-        <v>11</v>
+        <f>TestCoverage!B8</f>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <f>TestCoverage!A8 &amp; " (" &amp; TestCoverage!B8 &amp; ")"</f>
-        <v>User Access &amp; Permissions (1)</v>
+        <f>TestCoverage!A9 &amp; " (" &amp; TestCoverage!B9 &amp; ")"</f>
+        <v>Assignment &amp; Routing (4)</v>
       </c>
       <c r="B8" s="3">
-        <f>TestCoverage!F8</f>
+        <f>TestCoverage!F9</f>
         <v>1</v>
       </c>
       <c r="C8" s="3">
-        <f>TestCoverage!G8</f>
+        <f>TestCoverage!G9</f>
         <v>0</v>
       </c>
       <c r="D8" s="3">
-        <f>TestCoverage!H8</f>
+        <f>TestCoverage!H9</f>
         <v>0</v>
       </c>
       <c r="E8" s="3">
@@ -2727,18 +2882,18 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <f>TestCoverage!B8</f>
-        <v>1</v>
+        <f>TestCoverage!B9</f>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>TestCoverage!A10 &amp; " (" &amp; TestCoverage!B10 &amp; ")"</f>
-        <v>API End To End ()</v>
+        <v>API End To End (4)</v>
       </c>
       <c r="B9" s="3">
         <f>TestCoverage!F10</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3">
         <f>TestCoverage!G10</f>
@@ -2749,66 +2904,196 @@
         <v>0</v>
       </c>
       <c r="E9" s="3">
-        <f>C10 + D10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F9">
         <f>TestCoverage!B10</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
-        <f>TestCoverage!A9 &amp; " (" &amp; TestCoverage!B9 &amp; ")"</f>
-        <v>Assignment &amp; Routing ()</v>
+        <f>TestCoverage!A11 &amp; " (" &amp; TestCoverage!B11 &amp; ")"</f>
+        <v>Search &amp; Filters (5)</v>
       </c>
       <c r="B10" s="3">
-        <f>TestCoverage!F9</f>
-        <v>0</v>
+        <f>TestCoverage!F11</f>
+        <v>1</v>
       </c>
       <c r="C10" s="3">
-        <f>TestCoverage!G9</f>
+        <f>TestCoverage!G11</f>
         <v>0</v>
       </c>
       <c r="D10" s="3">
-        <f>TestCoverage!H9</f>
+        <f>TestCoverage!H11</f>
         <v>0</v>
       </c>
       <c r="E10" s="3">
-        <f>C9 + D9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F10">
-        <f>TestCoverage!B9</f>
-        <v>0</v>
+        <f>TestCoverage!B11</f>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>TestCoverage!A12 &amp; " (" &amp; TestCoverage!B12 &amp; ")"</f>
-        <v>TOTAL (58)</v>
+        <v>Reporting &amp; Data Export (3)</v>
       </c>
       <c r="B11" s="3">
         <f>TestCoverage!F12</f>
-        <v>0.96551724137931039</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="C11" s="3">
         <f>TestCoverage!G12</f>
-        <v>3.4482758620689655E-2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="3">
         <f>TestCoverage!H12</f>
         <v>0</v>
       </c>
-      <c r="E11" s="3"/>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="F11">
         <f>TestCoverage!B12</f>
-        <v>58</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <f>TestCoverage!A13 &amp; " (" &amp; TestCoverage!B13 &amp; ")"</f>
+        <v>Accessibility (Section 508 Compliance) (4)</v>
+      </c>
+      <c r="B12" s="3">
+        <f>TestCoverage!F13</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <f>TestCoverage!G13</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <f>TestCoverage!H13</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>TestCoverage!B13</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <f>TestCoverage!A14 &amp; " (" &amp; TestCoverage!B14 &amp; ")"</f>
+        <v>Email Notifications &amp; Alerts (3)</v>
+      </c>
+      <c r="B13" s="3">
+        <f>TestCoverage!F14</f>
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="C13" s="3">
+        <f>TestCoverage!G14</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <f>TestCoverage!H14</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>TestCoverage!B14</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <f>TestCoverage!A15 &amp; " (" &amp; TestCoverage!B15 &amp; ")"</f>
+        <v>Timeline &amp; SLA Management (10)</v>
+      </c>
+      <c r="B14" s="3">
+        <f>TestCoverage!F15</f>
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <f>TestCoverage!G15</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <f>TestCoverage!H15</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f>TestCoverage!B15</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="str">
+        <f>TestCoverage!A16 &amp; " (" &amp; TestCoverage!B16 &amp; ")"</f>
+        <v>Document Management ()</v>
+      </c>
+      <c r="B15" s="3">
+        <f>TestCoverage!F16</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="3">
+        <f>TestCoverage!G16</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <f>TestCoverage!H16</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>TestCoverage!B16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="str">
+        <f>TestCoverage!A17 &amp; " (" &amp; TestCoverage!B17 &amp; ")"</f>
+        <v>TOTAL (90)</v>
+      </c>
+      <c r="B16" s="3">
+        <f>TestCoverage!F17</f>
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="C16" s="3">
+        <f>TestCoverage!G17</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <f>TestCoverage!H17</f>
+        <v>2.2222222222222223E-2</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16">
+        <f>TestCoverage!B17</f>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F11">
-    <sortCondition descending="1" ref="E2:E11"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F16">
+    <sortCondition descending="1" ref="E13:E16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/TestCoverageDashboard_QA.xlsx
+++ b/src/test/resources/TestCoverageDashboard_QA.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB125AE9-DB5A-430F-A1BB-F3D1FF852B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2B0BF4-F9A7-400B-8F68-D85C6A0E3E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCoverage" sheetId="1" r:id="rId1"/>
     <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
-    <sheet name="Dashboard_Data" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Dashboard_Data" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Dashboard_Data!$A$1:$F$16</definedName>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>Functional Area</t>
   </si>
@@ -144,6 +144,9 @@
   <si>
     <t>Document Management</t>
   </si>
+  <si>
+    <t>Pending Automation %</t>
+  </si>
 </sst>
 </file>
 
@@ -153,7 +156,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,8 +218,15 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -232,12 +242,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCE6F1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -302,57 +306,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -361,20 +372,91 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEF8C5B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFF8696B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF5050"/>
+      <color rgb="FFFFFF66"/>
+      <color rgb="FFEF8C5B"/>
+      <color rgb="FFF8696B"/>
+      <color rgb="FFDAF2D0"/>
+      <color rgb="FFCC3300"/>
       <color rgb="FFFFFFFF"/>
       <color rgb="FFF7F7F7"/>
       <color rgb="FF4F81BD"/>
       <color rgb="FF1F4E79"/>
-      <color rgb="FFDCE6F1"/>
-      <color rgb="FFFFFFCC"/>
-      <color rgb="FFFF694B"/>
-      <color rgb="FFFF9D89"/>
-      <color rgb="FFFF5C3B"/>
-      <color rgb="FFFF5050"/>
     </mruColors>
   </colors>
   <extLst>
@@ -409,7 +491,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -422,7 +504,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1400" b="1">
+              <a:rPr lang="en-US" sz="1600" b="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -447,7 +529,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -499,7 +581,60 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -507,46 +642,46 @@
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>RAI Management (4)</c:v>
+                  <c:v>RAI Management (3)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Validations &amp; Business Rules (33)</c:v>
+                  <c:v>SRT Review Workflow ()</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>SRT Review Workflow (5)</c:v>
+                  <c:v>Workflow &amp; Status Transitions (7)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
+                  <c:v>Record Lifecycle Management (17)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Record Lifecycle Management (11)</c:v>
+                  <c:v>User Access &amp; Permissions (1)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
+                  <c:v>Assignment &amp; Routing (8)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Assignment &amp; Routing (4)</c:v>
+                  <c:v>API End To End ()</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>API End To End (4)</c:v>
+                  <c:v>Search &amp; Filters ()</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Search &amp; Filters (5)</c:v>
+                  <c:v>Reporting &amp; Data Export ()</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Reporting &amp; Data Export (3)</c:v>
+                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Accessibility (Section 508 Compliance) (4)</c:v>
+                  <c:v>Email Notifications &amp; Alerts ()</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Email Notifications &amp; Alerts (3)</c:v>
+                  <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Timeline &amp; SLA Management (10)</c:v>
+                  <c:v>Document Management ()</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Document Management ()</c:v>
+                  <c:v>Validations &amp; Business Rules (25)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -558,10 +693,10 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0.5</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.93939393939393945</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -576,28 +711,28 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.3333333333333333</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.3333333333333333</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.76</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -633,7 +768,60 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -641,46 +829,46 @@
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>RAI Management (4)</c:v>
+                  <c:v>RAI Management (3)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Validations &amp; Business Rules (33)</c:v>
+                  <c:v>SRT Review Workflow ()</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>SRT Review Workflow (5)</c:v>
+                  <c:v>Workflow &amp; Status Transitions (7)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
+                  <c:v>Record Lifecycle Management (17)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Record Lifecycle Management (11)</c:v>
+                  <c:v>User Access &amp; Permissions (1)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
+                  <c:v>Assignment &amp; Routing (8)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Assignment &amp; Routing (4)</c:v>
+                  <c:v>API End To End ()</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>API End To End (4)</c:v>
+                  <c:v>Search &amp; Filters ()</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Search &amp; Filters (5)</c:v>
+                  <c:v>Reporting &amp; Data Export ()</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Reporting &amp; Data Export (3)</c:v>
+                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Accessibility (Section 508 Compliance) (4)</c:v>
+                  <c:v>Email Notifications &amp; Alerts ()</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Email Notifications &amp; Alerts (3)</c:v>
+                  <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Timeline &amp; SLA Management (10)</c:v>
+                  <c:v>Document Management ()</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Document Management ()</c:v>
+                  <c:v>Validations &amp; Business Rules (25)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -695,7 +883,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.0606060606060608E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -731,7 +919,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>0.24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -767,7 +955,60 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:delete val="1"/>
+            <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -775,46 +1016,46 @@
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>RAI Management (4)</c:v>
+                  <c:v>RAI Management (3)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Validations &amp; Business Rules (33)</c:v>
+                  <c:v>SRT Review Workflow ()</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>SRT Review Workflow (5)</c:v>
+                  <c:v>Workflow &amp; Status Transitions (7)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Workflow &amp; Status Transitions (3)</c:v>
+                  <c:v>Record Lifecycle Management (17)</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Record Lifecycle Management (11)</c:v>
+                  <c:v>User Access &amp; Permissions (1)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
+                  <c:v>Assignment &amp; Routing (8)</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Assignment &amp; Routing (4)</c:v>
+                  <c:v>API End To End ()</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>API End To End (4)</c:v>
+                  <c:v>Search &amp; Filters ()</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Search &amp; Filters (5)</c:v>
+                  <c:v>Reporting &amp; Data Export ()</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Reporting &amp; Data Export (3)</c:v>
+                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Accessibility (Section 508 Compliance) (4)</c:v>
+                  <c:v>Email Notifications &amp; Alerts ()</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Email Notifications &amp; Alerts (3)</c:v>
+                  <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Timeline &amp; SLA Management (10)</c:v>
+                  <c:v>Document Management ()</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Document Management ()</c:v>
+                  <c:v>Validations &amp; Business Rules (25)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -826,7 +1067,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -873,6 +1114,193 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-FB6E-45FE-8991-B3D9A8DE49D8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard_Data!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Pending Automation %</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="bg2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>RAI Management (3)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>SRT Review Workflow ()</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Workflow &amp; Status Transitions (7)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Record Lifecycle Management (17)</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>User Access &amp; Permissions (1)</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Assignment &amp; Routing (8)</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>API End To End ()</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Search &amp; Filters ()</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Reporting &amp; Data Export ()</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Email Notifications &amp; Alerts ()</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Timeline &amp; SLA Management (10)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Document Management ()</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Validations &amp; Business Rules (25)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard_Data!$G$2:$G$15</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-29EC-408F-AD2C-7EC024EDF909}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -919,12 +1347,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -966,12 +1391,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="tx1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1001,7 +1423,7 @@
           <c:yMode val="edge"/>
           <c:x val="0.46588824688972519"/>
           <c:y val="0.9143754541065745"/>
-          <c:w val="0.17214009171974623"/>
+          <c:w val="0.30556385581748019"/>
           <c:h val="7.9481106747818109E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -1018,12 +1440,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1630,13 +2049,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>209000</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>144432</xdr:rowOff>
+      <xdr:rowOff>144431</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>227134</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>87924</xdr:rowOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>66260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1986,533 +2405,476 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.140625" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" customWidth="1"/>
+    <col min="1" max="1" width="32.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" customWidth="1"/>
     <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="22">
-        <v>46094.503644780096</v>
-      </c>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="24">
+        <v>46098.618946759256</v>
+      </c>
+      <c r="D1" s="25"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="11" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="14">
-        <v>33</v>
-      </c>
-      <c r="C3" s="14">
-        <v>31</v>
-      </c>
-      <c r="D3" s="14">
-        <v>2</v>
-      </c>
-      <c r="E3" s="14">
-        <v>0</v>
-      </c>
-      <c r="F3" s="11">
-        <f>IFERROR(C3/B3,0)</f>
-        <v>0.93939393939393945</v>
-      </c>
-      <c r="G3" s="11">
+      <c r="B3" s="9">
+        <v>25</v>
+      </c>
+      <c r="C3" s="9">
+        <v>19</v>
+      </c>
+      <c r="D3" s="9">
+        <v>6</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
+        <f>IF(B3=0,"",C3/B3)</f>
+        <v>0.76</v>
+      </c>
+      <c r="G3" s="7">
         <f>IFERROR(D3/B3,0)</f>
-        <v>6.0606060606060608E-2</v>
-      </c>
-      <c r="H3" s="11">
+        <v>0.24</v>
+      </c>
+      <c r="H3" s="7">
         <f>IFERROR(E3/B3,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="15">
-        <v>4</v>
-      </c>
-      <c r="C4" s="15">
-        <v>2</v>
-      </c>
-      <c r="D4" s="15">
-        <v>0</v>
-      </c>
-      <c r="E4" s="15">
-        <v>2</v>
-      </c>
-      <c r="F4" s="11">
-        <f t="shared" ref="F4:F16" si="0">IFERROR(C4/B4,0)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G4" s="11">
+      <c r="B4" s="10">
+        <v>3</v>
+      </c>
+      <c r="C4" s="10">
+        <v>3</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
+        <f t="shared" ref="F4:F16" si="0">IF(B4=0,"",C4/B4)</f>
+        <v>1</v>
+      </c>
+      <c r="G4" s="7">
         <f t="shared" ref="G4:G14" si="1">IFERROR(D4/B4,0)</f>
         <v>0</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="7">
         <f t="shared" ref="H4:H14" si="2">IFERROR(E4/B4,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="14">
-        <v>5</v>
-      </c>
-      <c r="C5" s="14">
-        <v>5</v>
-      </c>
-      <c r="D5" s="14">
-        <v>0</v>
-      </c>
-      <c r="E5" s="14">
-        <v>0</v>
-      </c>
-      <c r="F5" s="11">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="10">
+        <v>7</v>
+      </c>
+      <c r="C6" s="10">
+        <v>7</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G6" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H6" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="15">
-        <v>3</v>
-      </c>
-      <c r="C6" s="15">
-        <v>3</v>
-      </c>
-      <c r="D6" s="15">
-        <v>0</v>
-      </c>
-      <c r="E6" s="15">
-        <v>0</v>
-      </c>
-      <c r="F6" s="11">
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="9">
+        <v>17</v>
+      </c>
+      <c r="C7" s="9">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G7" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H7" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="14">
-        <v>11</v>
-      </c>
-      <c r="C7" s="14">
-        <v>11</v>
-      </c>
-      <c r="D7" s="14">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14">
-        <v>0</v>
-      </c>
-      <c r="F7" s="11">
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="9">
+        <v>1</v>
+      </c>
+      <c r="C8" s="10">
+        <v>1</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G8" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H8" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="15">
-        <v>1</v>
-      </c>
-      <c r="C8" s="15">
-        <v>1</v>
-      </c>
-      <c r="D8" s="15">
-        <v>0</v>
-      </c>
-      <c r="E8" s="15">
-        <v>0</v>
-      </c>
-      <c r="F8" s="11">
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G9" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H9" s="7">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="14">
-        <v>4</v>
-      </c>
-      <c r="C9" s="14">
-        <v>4</v>
-      </c>
-      <c r="D9" s="14">
-        <v>0</v>
-      </c>
-      <c r="E9" s="14">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G10" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G12" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G13" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="7" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="9">
+        <v>10</v>
+      </c>
+      <c r="C15" s="9">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G9" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="15">
-        <v>4</v>
-      </c>
-      <c r="C10" s="15">
-        <v>4</v>
-      </c>
-      <c r="D10" s="15">
-        <v>0</v>
-      </c>
-      <c r="E10" s="15">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11">
+      <c r="G15" s="7">
+        <f>IFERROR(D15/B15,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" ref="H15:H17" si="3">IFERROR(E15/B15,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="7" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G10" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="14">
-        <v>5</v>
-      </c>
-      <c r="C11" s="14">
-        <v>5</v>
-      </c>
-      <c r="D11" s="14">
-        <v>0</v>
-      </c>
-      <c r="E11" s="14">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G11" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="15">
-        <v>3</v>
-      </c>
-      <c r="C12" s="15">
-        <v>4</v>
-      </c>
-      <c r="D12" s="15">
-        <v>0</v>
-      </c>
-      <c r="E12" s="15">
-        <v>0</v>
-      </c>
-      <c r="F12" s="11">
-        <f t="shared" si="0"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="G12" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="14">
-        <v>4</v>
-      </c>
-      <c r="C13" s="14">
-        <v>4</v>
-      </c>
-      <c r="D13" s="14">
-        <v>0</v>
-      </c>
-      <c r="E13" s="14">
-        <v>0</v>
-      </c>
-      <c r="F13" s="11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G13" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="15">
-        <v>3</v>
-      </c>
-      <c r="C14" s="15">
-        <v>4</v>
-      </c>
-      <c r="D14" s="15">
-        <v>0</v>
-      </c>
-      <c r="E14" s="15">
-        <v>0</v>
-      </c>
-      <c r="F14" s="11">
-        <f t="shared" si="0"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="G14" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="11">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="14">
-        <v>10</v>
-      </c>
-      <c r="C15" s="14">
-        <v>10</v>
-      </c>
-      <c r="D15" s="14">
-        <v>0</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
-      </c>
-      <c r="F15" s="11">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G15" s="11">
-        <f>IFERROR(D15/B15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="11">
-        <f t="shared" ref="H15:H17" si="3">IFERROR(E15/B15,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G16" s="11">
+        <v/>
+      </c>
+      <c r="G16" s="7">
         <f>IFERROR(D16/B16,0)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="7">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="16">
-        <f>SUM(B3:B15)</f>
-        <v>90</v>
-      </c>
-      <c r="C17" s="16">
+      <c r="B17" s="15">
+        <f>SUM(B3:B16)</f>
+        <v>71</v>
+      </c>
+      <c r="C17" s="15">
         <f>SUM(C3:C15)</f>
-        <v>88</v>
-      </c>
-      <c r="D17" s="16">
+        <v>65</v>
+      </c>
+      <c r="D17" s="15">
         <f>SUM(D3:D15)</f>
-        <v>2</v>
-      </c>
-      <c r="E17" s="16">
+        <v>6</v>
+      </c>
+      <c r="E17" s="15">
         <f>SUM(E3:E15)</f>
-        <v>2</v>
-      </c>
-      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="16">
         <f t="shared" ref="F17" si="4">IFERROR(C17/B17,0)</f>
-        <v>0.97777777777777775</v>
-      </c>
-      <c r="G17" s="5">
+        <v>0.91549295774647887</v>
+      </c>
+      <c r="G17" s="16">
         <f t="shared" ref="G17" si="5">IFERROR(D17/B17,0)</f>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="H17" s="5">
+        <v>8.4507042253521125E-2</v>
+      </c>
+      <c r="H17" s="16">
         <f t="shared" si="3"/>
-        <v>2.2222222222222223E-2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F3:F17">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="F3:F16">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.6"/>
         <cfvo type="num" val="1"/>
-        <color rgb="FFFF5050"/>
-        <color rgb="FFFFFF00"/>
-        <color theme="9" tint="0.59999389629810485"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFDAF2D0"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G17">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="1"/>
-        <color theme="9" tint="0.59999389629810485"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FFFF5050"/>
-      </colorScale>
+  <conditionalFormatting sqref="G3:G16">
+    <cfRule type="cellIs" dxfId="9" priority="4" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="num" val="0"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="1"/>
-        <color theme="9" tint="0.59999389629810485"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FFFF5050"/>
-      </colorScale>
+  <conditionalFormatting sqref="G3:H16">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H16">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThan">
+      <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2534,139 +2896,167 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
     </row>
     <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="9" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="9">
-        <f>TestCoverage!B1</f>
-        <v>46094.503644780096</v>
-      </c>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
+      <c r="F2" s="5">
+        <f>TestCoverage!C1</f>
+        <v>46098.618946759256</v>
+      </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="18" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="18">
         <f>TestCoverage!B17</f>
-        <v>90</v>
-      </c>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
+        <v>71</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
     </row>
     <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="20" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="18">
         <f>TestCoverage!C17</f>
-        <v>88</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
+        <v>65</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="20" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="18">
         <f>TestCoverage!D17</f>
-        <v>2</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
+        <v>6</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="20" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <f>TestCoverage!E17</f>
-        <v>2</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
     </row>
     <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="20" t="s">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="21">
-        <f>TestCoverage!C17/TestCoverage!B17</f>
-        <v>0.97777777777777775</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="F7" s="17">
+        <f>IFERROR(F4/F3,"")</f>
+        <v>0.91549295774647887</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>
+  <conditionalFormatting sqref="E5:F5">
+    <cfRule type="expression" dxfId="6" priority="1">
+      <formula>$F$5&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>$F$5=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:F6">
+    <cfRule type="expression" dxfId="4" priority="3">
+      <formula>$F$6&gt;0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$F$6=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:F7">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="lessThan">
+      <formula>0.6</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="6" operator="between">
+      <formula>0.6</formula>
+      <formula>0.79</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="greaterThanOrEqual">
+      <formula>0.8</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2675,425 +3065,489 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC817E08-797F-444D-BF6E-D4C8FC527215}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.85546875" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="4" max="5" width="13.85546875" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="22" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="str">
+      <c r="G1" s="22" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="20" t="str">
         <f>TestCoverage!A4 &amp; " (" &amp; TestCoverage!B4 &amp; ")"</f>
-        <v>RAI Management (4)</v>
-      </c>
-      <c r="B2" s="3">
+        <v>RAI Management (3)</v>
+      </c>
+      <c r="B2" s="21">
         <f>TestCoverage!F4</f>
-        <v>0.5</v>
-      </c>
-      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="21">
         <f>TestCoverage!G4</f>
         <v>0</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="21">
         <f>TestCoverage!H4</f>
-        <v>0.5</v>
-      </c>
-      <c r="E2" s="3">
-        <f t="shared" ref="E2:E15" si="0">C2 + D2</f>
-        <v>0.5</v>
-      </c>
-      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="21">
+        <f>C2 + D2</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="20">
         <f>TestCoverage!B4</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <f>TestCoverage!A3 &amp; " (" &amp; TestCoverage!B3 &amp; ")"</f>
-        <v>Validations &amp; Business Rules (33)</v>
-      </c>
-      <c r="B3" s="3">
-        <f>TestCoverage!F3</f>
-        <v>0.93939393939393945</v>
-      </c>
-      <c r="C3" s="3">
-        <f>TestCoverage!G3</f>
-        <v>6.0606060606060608E-2</v>
-      </c>
-      <c r="D3" s="3">
-        <f>TestCoverage!H3</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <f t="shared" si="0"/>
-        <v>6.0606060606060608E-2</v>
-      </c>
-      <c r="F3">
-        <f>TestCoverage!B3</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="G2" s="19">
+        <f>IF($F2=0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="str">
         <f>TestCoverage!A5 &amp; " (" &amp; TestCoverage!B5 &amp; ")"</f>
-        <v>SRT Review Workflow (5)</v>
-      </c>
-      <c r="B4" s="3">
+        <v>SRT Review Workflow ()</v>
+      </c>
+      <c r="B3" s="21" t="str">
         <f>TestCoverage!F5</f>
+        <v/>
+      </c>
+      <c r="C3" s="21">
+        <f>TestCoverage!G5</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="21">
+        <f>TestCoverage!H5</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="21">
+        <f>C3 + D3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="20">
+        <f>TestCoverage!B5</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="19">
+        <f>IF($F3=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C4" s="3">
-        <f>TestCoverage!G5</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <f>TestCoverage!H5</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <f>TestCoverage!B5</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="str">
+    </row>
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="str">
         <f>TestCoverage!A6 &amp; " (" &amp; TestCoverage!B6 &amp; ")"</f>
-        <v>Workflow &amp; Status Transitions (3)</v>
-      </c>
-      <c r="B5" s="3">
+        <v>Workflow &amp; Status Transitions (7)</v>
+      </c>
+      <c r="B4" s="21">
         <f>TestCoverage!F6</f>
         <v>1</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C4" s="21">
         <f>TestCoverage!G6</f>
         <v>0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D4" s="21">
         <f>TestCoverage!H6</f>
         <v>0</v>
       </c>
-      <c r="E5" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F5">
+      <c r="E4" s="21">
+        <f>C4 + D4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="20">
         <f>TestCoverage!B6</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
+        <v>7</v>
+      </c>
+      <c r="G4" s="19">
+        <f>IF($F4=0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="str">
         <f>TestCoverage!A7 &amp; " (" &amp; TestCoverage!B7 &amp; ")"</f>
-        <v>Record Lifecycle Management (11)</v>
-      </c>
-      <c r="B6" s="3">
+        <v>Record Lifecycle Management (17)</v>
+      </c>
+      <c r="B5" s="21">
         <f>TestCoverage!F7</f>
         <v>1</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C5" s="21">
         <f>TestCoverage!G7</f>
         <v>0</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D5" s="21">
         <f>TestCoverage!H7</f>
         <v>0</v>
       </c>
-      <c r="E6" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6">
+      <c r="E5" s="21">
+        <f>C5 + D5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="20">
         <f>TestCoverage!B7</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="str">
+        <v>17</v>
+      </c>
+      <c r="G5" s="19">
+        <f>IF($F5=0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="str">
         <f>TestCoverage!A8 &amp; " (" &amp; TestCoverage!B8 &amp; ")"</f>
         <v>User Access &amp; Permissions (1)</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B6" s="21">
         <f>TestCoverage!F8</f>
         <v>1</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C6" s="21">
         <f>TestCoverage!G8</f>
         <v>0</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D6" s="21">
         <f>TestCoverage!H8</f>
         <v>0</v>
       </c>
-      <c r="E7" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F7">
+      <c r="E6" s="21">
+        <f>C6 + D6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="20">
         <f>TestCoverage!B8</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="str">
+      <c r="G6" s="19">
+        <f>IF($F6=0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="str">
         <f>TestCoverage!A9 &amp; " (" &amp; TestCoverage!B9 &amp; ")"</f>
-        <v>Assignment &amp; Routing (4)</v>
-      </c>
-      <c r="B8" s="3">
+        <v>Assignment &amp; Routing (8)</v>
+      </c>
+      <c r="B7" s="21">
         <f>TestCoverage!F9</f>
         <v>1</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C7" s="21">
         <f>TestCoverage!G9</f>
         <v>0</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D7" s="21">
         <f>TestCoverage!H9</f>
         <v>0</v>
       </c>
-      <c r="E8" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F8">
+      <c r="E7" s="21">
+        <f>C7 + D7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="20">
         <f>TestCoverage!B9</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="str">
+        <v>8</v>
+      </c>
+      <c r="G7" s="19">
+        <f>IF($F7=0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="str">
         <f>TestCoverage!A10 &amp; " (" &amp; TestCoverage!B10 &amp; ")"</f>
-        <v>API End To End (4)</v>
-      </c>
-      <c r="B9" s="3">
+        <v>API End To End ()</v>
+      </c>
+      <c r="B8" s="21" t="str">
         <f>TestCoverage!F10</f>
+        <v/>
+      </c>
+      <c r="C8" s="21">
+        <f>TestCoverage!G10</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="21">
+        <f>TestCoverage!H10</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="21">
+        <f>C8 + D8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="20">
+        <f>TestCoverage!B10</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="19">
+        <f>IF($F8=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C9" s="3">
-        <f>TestCoverage!G10</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <f>TestCoverage!H10</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <f>TestCoverage!B10</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="str">
+    </row>
+    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="str">
         <f>TestCoverage!A11 &amp; " (" &amp; TestCoverage!B11 &amp; ")"</f>
-        <v>Search &amp; Filters (5)</v>
-      </c>
-      <c r="B10" s="3">
+        <v>Search &amp; Filters ()</v>
+      </c>
+      <c r="B9" s="21" t="str">
         <f>TestCoverage!F11</f>
+        <v/>
+      </c>
+      <c r="C9" s="21">
+        <f>TestCoverage!G11</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="21">
+        <f>TestCoverage!H11</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="21">
+        <f>C9 + D9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="20">
+        <f>TestCoverage!B11</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="19">
+        <f>IF($F9=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="3">
-        <f>TestCoverage!G11</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="3">
-        <f>TestCoverage!H11</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <f>TestCoverage!B11</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="str">
+    </row>
+    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="str">
         <f>TestCoverage!A12 &amp; " (" &amp; TestCoverage!B12 &amp; ")"</f>
-        <v>Reporting &amp; Data Export (3)</v>
-      </c>
-      <c r="B11" s="3">
+        <v>Reporting &amp; Data Export ()</v>
+      </c>
+      <c r="B10" s="21" t="str">
         <f>TestCoverage!F12</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="C11" s="3">
+        <v/>
+      </c>
+      <c r="C10" s="21">
         <f>TestCoverage!G12</f>
         <v>0</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D10" s="21">
         <f>TestCoverage!H12</f>
         <v>0</v>
       </c>
-      <c r="E11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F11">
+      <c r="E10" s="21">
+        <f>C10 + D10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="20">
         <f>TestCoverage!B12</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="str">
+        <v>0</v>
+      </c>
+      <c r="G10" s="19">
+        <f>IF($F10=0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="str">
         <f>TestCoverage!A13 &amp; " (" &amp; TestCoverage!B13 &amp; ")"</f>
-        <v>Accessibility (Section 508 Compliance) (4)</v>
-      </c>
-      <c r="B12" s="3">
+        <v>Accessibility (Section 508 Compliance) ()</v>
+      </c>
+      <c r="B11" s="21" t="str">
         <f>TestCoverage!F13</f>
+        <v/>
+      </c>
+      <c r="C11" s="21">
+        <f>TestCoverage!G13</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="21">
+        <f>TestCoverage!H13</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="21">
+        <f>C11 + D11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="20">
+        <f>TestCoverage!B13</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="19">
+        <f>IF($F11=0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="C12" s="3">
-        <f>TestCoverage!G13</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="3">
-        <f>TestCoverage!H13</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <f>TestCoverage!B13</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
+    </row>
+    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="str">
         <f>TestCoverage!A14 &amp; " (" &amp; TestCoverage!B14 &amp; ")"</f>
-        <v>Email Notifications &amp; Alerts (3)</v>
-      </c>
-      <c r="B13" s="3">
+        <v>Email Notifications &amp; Alerts ()</v>
+      </c>
+      <c r="B12" s="21" t="str">
         <f>TestCoverage!F14</f>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="C13" s="3">
+        <v/>
+      </c>
+      <c r="C12" s="21">
         <f>TestCoverage!G14</f>
         <v>0</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D12" s="21">
         <f>TestCoverage!H14</f>
         <v>0</v>
       </c>
-      <c r="E13" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F13">
+      <c r="E12" s="21">
+        <f>C12 + D12</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="20">
         <f>TestCoverage!B14</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="str">
+        <v>0</v>
+      </c>
+      <c r="G12" s="19">
+        <f>IF($F12=0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="str">
         <f>TestCoverage!A15 &amp; " (" &amp; TestCoverage!B15 &amp; ")"</f>
         <v>Timeline &amp; SLA Management (10)</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B13" s="21">
         <f>TestCoverage!F15</f>
         <v>1</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C13" s="21">
         <f>TestCoverage!G15</f>
         <v>0</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D13" s="21">
         <f>TestCoverage!H15</f>
         <v>0</v>
       </c>
-      <c r="E14" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F14">
+      <c r="E13" s="21">
+        <f>C13 + D13</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="20">
         <f>TestCoverage!B15</f>
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="str">
+      <c r="G13" s="19">
+        <f>IF($F13=0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="str">
         <f>TestCoverage!A16 &amp; " (" &amp; TestCoverage!B16 &amp; ")"</f>
         <v>Document Management ()</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B14" s="21" t="str">
         <f>TestCoverage!F16</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="3">
+        <v/>
+      </c>
+      <c r="C14" s="21">
         <f>TestCoverage!G16</f>
         <v>0</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D14" s="21">
         <f>TestCoverage!H16</f>
         <v>0</v>
       </c>
-      <c r="E15" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F15">
+      <c r="E14" s="21">
+        <f>C14 + D14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="20">
         <f>TestCoverage!B16</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="str">
+      <c r="G14" s="19">
+        <f>IF($F14=0,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="str">
+        <f>TestCoverage!A3 &amp; " (" &amp; TestCoverage!B3 &amp; ")"</f>
+        <v>Validations &amp; Business Rules (25)</v>
+      </c>
+      <c r="B15" s="21">
+        <f>TestCoverage!F3</f>
+        <v>0.76</v>
+      </c>
+      <c r="C15" s="21">
+        <f>TestCoverage!G3</f>
+        <v>0.24</v>
+      </c>
+      <c r="D15" s="21">
+        <f>TestCoverage!H3</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="21">
+        <f>C15 + D15</f>
+        <v>0.24</v>
+      </c>
+      <c r="F15" s="20">
+        <f>TestCoverage!B3</f>
+        <v>25</v>
+      </c>
+      <c r="G15" s="19">
+        <f>IF($F15=0,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="20" t="str">
         <f>TestCoverage!A17 &amp; " (" &amp; TestCoverage!B17 &amp; ")"</f>
-        <v>TOTAL (90)</v>
-      </c>
-      <c r="B16" s="3">
+        <v>TOTAL (71)</v>
+      </c>
+      <c r="B16" s="21">
         <f>TestCoverage!F17</f>
-        <v>0.97777777777777775</v>
-      </c>
-      <c r="C16" s="3">
+        <v>0.91549295774647887</v>
+      </c>
+      <c r="C16" s="21">
         <f>TestCoverage!G17</f>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="D16" s="3">
+        <v>8.4507042253521125E-2</v>
+      </c>
+      <c r="D16" s="21">
         <f>TestCoverage!H17</f>
-        <v>2.2222222222222223E-2</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="20">
         <f>TestCoverage!B17</f>
-        <v>90</v>
+        <v>71</v>
+      </c>
+      <c r="G16" s="19">
+        <f>COUNTIF(F2:F14,0)/COUNTA(A2:A14)</f>
+        <v>0.53846153846153844</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F16">
-    <sortCondition descending="1" ref="E13:E16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
+    <sortCondition ref="E2:E16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/TestCoverageDashboard_QA.xlsx
+++ b/src/test/resources/TestCoverageDashboard_QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2B0BF4-F9A7-400B-8F68-D85C6A0E3E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F99EDB-2C30-4BDD-AF16-39FB360AD3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCoverage" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>Functional Area</t>
   </si>
@@ -152,9 +152,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="m/d/yyyy h:mm:ss AM/PM"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -306,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -368,6 +369,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,7 +683,7 @@
                   <c:v>Document Management ()</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (25)</c:v>
+                  <c:v>Validations &amp; Business Rules (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -702,7 +704,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0.94117647058823528</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -726,13 +728,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.76</c:v>
+                  <c:v>0.93333333333333335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -868,7 +870,7 @@
                   <c:v>Document Management ()</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (25)</c:v>
+                  <c:v>Validations &amp; Business Rules (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -889,7 +891,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>5.8823529411764705E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -913,13 +915,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.24</c:v>
+                  <c:v>6.6666666666666666E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1055,7 +1057,7 @@
                   <c:v>Document Management ()</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (25)</c:v>
+                  <c:v>Validations &amp; Business Rules (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1133,7 +1135,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg2"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1242,7 +1246,7 @@
                   <c:v>Document Management ()</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (25)</c:v>
+                  <c:v>Validations &amp; Business Rules (30)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2405,15 +2409,15 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" customWidth="1"/>
-    <col min="6" max="6" width="8.140625" customWidth="1"/>
-    <col min="7" max="7" width="7.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="32.5703125"/>
+    <col min="2" max="2" customWidth="true" width="24.0"/>
+    <col min="3" max="3" customWidth="true" width="24.5703125"/>
+    <col min="4" max="4" customWidth="true" width="14.7109375"/>
+    <col min="5" max="5" customWidth="true" width="9.140625"/>
+    <col min="6" max="6" customWidth="true" width="8.140625"/>
+    <col min="7" max="7" customWidth="true" width="7.140625"/>
+    <col min="8" max="8" customWidth="true" width="11.28515625"/>
+    <col min="9" max="9" customWidth="true" width="24.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2421,8 +2425,8 @@
         <v>28</v>
       </c>
       <c r="B1" s="23"/>
-      <c r="C1" s="24">
-        <v>46098.618946759256</v>
+      <c r="C1" s="27" t="n">
+        <v>46105.66914611111</v>
       </c>
       <c r="D1" s="25"/>
       <c r="E1" s="23"/>
@@ -2460,58 +2464,58 @@
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="9">
-        <v>25</v>
-      </c>
-      <c r="C3" s="9">
-        <v>19</v>
-      </c>
-      <c r="D3" s="9">
-        <v>6</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="B3" s="9" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="7" t="n">
         <f>IF(B3=0,"",C3/B3)</f>
-        <v>0.76</v>
-      </c>
-      <c r="G3" s="7">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="G3" s="7" t="n">
         <f>IFERROR(D3/B3,0)</f>
-        <v>0.24</v>
-      </c>
-      <c r="H3" s="7">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="H3" s="7" t="n">
         <f>IFERROR(E3/B3,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="10">
-        <v>3</v>
-      </c>
-      <c r="C4" s="10">
-        <v>3</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="B4" s="10" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <f t="shared" ref="F4:F16" si="0">IF(B4=0,"",C4/B4)</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G4" s="7" t="n">
         <f t="shared" ref="G4:G14" si="1">IFERROR(D4/B4,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="7" t="n">
         <f t="shared" ref="H4:H14" si="2">IFERROR(E4/B4,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
@@ -2526,129 +2530,129 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H5" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="10">
-        <v>7</v>
-      </c>
-      <c r="C6" s="10">
-        <v>7</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0</v>
-      </c>
-      <c r="E6" s="10">
-        <v>0</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="B6" s="10" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9">
-        <v>17</v>
-      </c>
-      <c r="C7" s="9">
-        <v>17</v>
-      </c>
-      <c r="D7" s="9">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0</v>
-      </c>
-      <c r="F7" s="7">
+      <c r="B7" s="9" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G7" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9">
-        <v>1</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="B8" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G8" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="9">
-        <v>8</v>
-      </c>
-      <c r="C9" s="9">
-        <v>8</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="B9" s="9" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I9" s="2"/>
     </row>
@@ -2664,13 +2668,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I10" s="2"/>
     </row>
@@ -2686,13 +2690,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I11" s="2"/>
     </row>
@@ -2708,13 +2712,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I12" s="2"/>
     </row>
@@ -2730,13 +2734,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I13" s="2"/>
     </row>
@@ -2752,13 +2756,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="7" t="n">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="7" t="n">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="I14" s="2"/>
     </row>
@@ -2766,29 +2770,29 @@
       <c r="A15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="9">
-        <v>10</v>
-      </c>
-      <c r="C15" s="9">
-        <v>10</v>
-      </c>
-      <c r="D15" s="9">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7">
+      <c r="B15" s="9" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <f>IFERROR(D15/B15,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="7" t="n">
         <f t="shared" ref="H15:H17" si="3">IFERROR(E15/B15,0)</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
@@ -2803,46 +2807,46 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="7" t="n">
         <f>IFERROR(D16/B16,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="7">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="7" t="n">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="15" t="n">
         <f>SUM(B3:B16)</f>
-        <v>71</v>
-      </c>
-      <c r="C17" s="15">
+        <v>76.0</v>
+      </c>
+      <c r="C17" s="15" t="n">
         <f>SUM(C3:C15)</f>
-        <v>65</v>
-      </c>
-      <c r="D17" s="15">
+        <v>74.0</v>
+      </c>
+      <c r="D17" s="15" t="n">
         <f>SUM(D3:D15)</f>
-        <v>6</v>
-      </c>
-      <c r="E17" s="15">
+        <v>2.0</v>
+      </c>
+      <c r="E17" s="15" t="n">
         <f>SUM(E3:E15)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="16">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="16" t="n">
         <f t="shared" ref="F17" si="4">IFERROR(C17/B17,0)</f>
-        <v>0.91549295774647887</v>
-      </c>
-      <c r="G17" s="16">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="G17" s="16" t="n">
         <f t="shared" ref="G17" si="5">IFERROR(D17/B17,0)</f>
-        <v>8.4507042253521125E-2</v>
-      </c>
-      <c r="H17" s="16">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="H17" s="16" t="n">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.0</v>
       </c>
     </row>
   </sheetData>
@@ -2887,12 +2891,12 @@
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="14.7109375"/>
+    <col min="2" max="2" customWidth="true" width="23.5703125"/>
+    <col min="5" max="5" customWidth="true" width="18.0"/>
+    <col min="6" max="6" customWidth="true" width="25.7109375"/>
+    <col min="7" max="7" customWidth="true" width="15.140625"/>
+    <col min="8" max="8" customWidth="true" width="10.5703125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30.75" x14ac:dyDescent="0.55000000000000004">
@@ -2919,9 +2923,9 @@
       <c r="E2" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="5" t="n">
         <f>TestCoverage!C1</f>
-        <v>46098.618946759256</v>
+        <v>46105.66914611111</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -2938,9 +2942,9 @@
       <c r="E3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F3" s="18" t="n">
         <f>TestCoverage!B17</f>
-        <v>71</v>
+        <v>76.0</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -2957,9 +2961,9 @@
       <c r="E4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="18" t="n">
         <f>TestCoverage!C17</f>
-        <v>65</v>
+        <v>74.0</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -2976,9 +2980,9 @@
       <c r="E5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="18" t="n">
         <f>TestCoverage!D17</f>
-        <v>6</v>
+        <v>2.0</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -2995,9 +2999,9 @@
       <c r="E6" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="18" t="n">
         <f>TestCoverage!E17</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -3014,9 +3018,9 @@
       <c r="E7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="17" t="n">
         <f>IFERROR(F4/F3,"")</f>
-        <v>0.91549295774647887</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -3068,11 +3072,11 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="4" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="37.85546875"/>
+    <col min="2" max="2" customWidth="true" width="14.0"/>
+    <col min="4" max="5" customWidth="true" width="13.85546875"/>
+    <col min="6" max="6" customWidth="true" width="10.42578125"/>
+    <col min="7" max="7" customWidth="true" width="26.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3103,29 +3107,29 @@
         <f>TestCoverage!A4 &amp; " (" &amp; TestCoverage!B4 &amp; ")"</f>
         <v>RAI Management (3)</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="21" t="n">
         <f>TestCoverage!F4</f>
-        <v>1</v>
-      </c>
-      <c r="C2" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="21" t="n">
         <f>TestCoverage!G4</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D2" s="21" t="n">
         <f>TestCoverage!H4</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="21">
-        <f>C2 + D2</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="21" t="n">
+        <f t="shared" ref="E2:E15" si="0">C2 + D2</f>
+        <v>0.0</v>
+      </c>
+      <c r="F2" s="20" t="n">
         <f>TestCoverage!B4</f>
-        <v>3</v>
-      </c>
-      <c r="G2" s="19">
-        <f>IF($F2=0,1,0)</f>
-        <v>0</v>
+        <v>3.0</v>
+      </c>
+      <c r="G2" s="19" t="n">
+        <f t="shared" ref="G2:G15" si="1">IF($F2=0,1,0)</f>
+        <v>0.0</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3137,25 +3141,25 @@
         <f>TestCoverage!F5</f>
         <v/>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="21" t="n">
         <f>TestCoverage!G5</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D3" s="21" t="n">
         <f>TestCoverage!H5</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="21">
-        <f>C3 + D3</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="20" t="n">
         <f>TestCoverage!B5</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="19">
-        <f>IF($F3=0,1,0)</f>
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>1.0</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3163,29 +3167,29 @@
         <f>TestCoverage!A6 &amp; " (" &amp; TestCoverage!B6 &amp; ")"</f>
         <v>Workflow &amp; Status Transitions (7)</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="21" t="n">
         <f>TestCoverage!F6</f>
-        <v>1</v>
-      </c>
-      <c r="C4" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="C4" s="21" t="n">
         <f>TestCoverage!G6</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="21" t="n">
         <f>TestCoverage!H6</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="21">
-        <f>C4 + D4</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="20" t="n">
         <f>TestCoverage!B6</f>
-        <v>7</v>
-      </c>
-      <c r="G4" s="19">
-        <f>IF($F4=0,1,0)</f>
-        <v>0</v>
+        <v>7.0</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3193,29 +3197,29 @@
         <f>TestCoverage!A7 &amp; " (" &amp; TestCoverage!B7 &amp; ")"</f>
         <v>Record Lifecycle Management (17)</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="21" t="n">
         <f>TestCoverage!F7</f>
-        <v>1</v>
-      </c>
-      <c r="C5" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="C5" s="21" t="n">
         <f>TestCoverage!G7</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D5" s="21" t="n">
         <f>TestCoverage!H7</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="21">
-        <f>C5 + D5</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="20" t="n">
         <f>TestCoverage!B7</f>
-        <v>17</v>
-      </c>
-      <c r="G5" s="19">
-        <f>IF($F5=0,1,0)</f>
-        <v>0</v>
+        <v>17.0</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3223,29 +3227,29 @@
         <f>TestCoverage!A8 &amp; " (" &amp; TestCoverage!B8 &amp; ")"</f>
         <v>User Access &amp; Permissions (1)</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="21" t="n">
         <f>TestCoverage!F8</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="C6" s="21" t="n">
         <f>TestCoverage!G8</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D6" s="21" t="n">
         <f>TestCoverage!H8</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="21">
-        <f>C6 + D6</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="20" t="n">
         <f>TestCoverage!B8</f>
-        <v>1</v>
-      </c>
-      <c r="G6" s="19">
-        <f>IF($F6=0,1,0)</f>
-        <v>0</v>
+        <v>1.0</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3253,29 +3257,29 @@
         <f>TestCoverage!A9 &amp; " (" &amp; TestCoverage!B9 &amp; ")"</f>
         <v>Assignment &amp; Routing (8)</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="21" t="n">
         <f>TestCoverage!F9</f>
-        <v>1</v>
-      </c>
-      <c r="C7" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="C7" s="21" t="n">
         <f>TestCoverage!G9</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="21" t="n">
         <f>TestCoverage!H9</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="21">
-        <f>C7 + D7</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="20" t="n">
         <f>TestCoverage!B9</f>
-        <v>8</v>
-      </c>
-      <c r="G7" s="19">
-        <f>IF($F7=0,1,0)</f>
-        <v>0</v>
+        <v>8.0</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3287,25 +3291,25 @@
         <f>TestCoverage!F10</f>
         <v/>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="21" t="n">
         <f>TestCoverage!G10</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="21" t="n">
         <f>TestCoverage!H10</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="21">
-        <f>C8 + D8</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="20" t="n">
         <f>TestCoverage!B10</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="19">
-        <f>IF($F8=0,1,0)</f>
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>1.0</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3317,25 +3321,25 @@
         <f>TestCoverage!F11</f>
         <v/>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="21" t="n">
         <f>TestCoverage!G11</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="21" t="n">
         <f>TestCoverage!H11</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="21">
-        <f>C9 + D9</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="20" t="n">
         <f>TestCoverage!B11</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="19">
-        <f>IF($F9=0,1,0)</f>
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>1.0</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3347,25 +3351,25 @@
         <f>TestCoverage!F12</f>
         <v/>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="21" t="n">
         <f>TestCoverage!G12</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="21" t="n">
         <f>TestCoverage!H12</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
-        <f>C10 + D10</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="20" t="n">
         <f>TestCoverage!B12</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="19">
-        <f>IF($F10=0,1,0)</f>
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>1.0</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3377,25 +3381,25 @@
         <f>TestCoverage!F13</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="21" t="n">
         <f>TestCoverage!G13</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="21" t="n">
         <f>TestCoverage!H13</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="21">
-        <f>C11 + D11</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F11" s="20" t="n">
         <f>TestCoverage!B13</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="19">
-        <f>IF($F11=0,1,0)</f>
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>1.0</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3407,25 +3411,25 @@
         <f>TestCoverage!F14</f>
         <v/>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="21" t="n">
         <f>TestCoverage!G14</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D12" s="21" t="n">
         <f>TestCoverage!H14</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="21">
-        <f>C12 + D12</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="20" t="n">
         <f>TestCoverage!B14</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="19">
-        <f>IF($F12=0,1,0)</f>
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>1.0</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3433,29 +3437,29 @@
         <f>TestCoverage!A15 &amp; " (" &amp; TestCoverage!B15 &amp; ")"</f>
         <v>Timeline &amp; SLA Management (10)</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="21" t="n">
         <f>TestCoverage!F15</f>
-        <v>1</v>
-      </c>
-      <c r="C13" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="C13" s="21" t="n">
         <f>TestCoverage!G15</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="21" t="n">
         <f>TestCoverage!H15</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="21">
-        <f>C13 + D13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="20" t="n">
         <f>TestCoverage!B15</f>
-        <v>10</v>
-      </c>
-      <c r="G13" s="19">
-        <f>IF($F13=0,1,0)</f>
-        <v>0</v>
+        <v>10.0</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
@@ -3467,82 +3471,82 @@
         <f>TestCoverage!F16</f>
         <v/>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="21" t="n">
         <f>TestCoverage!G16</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="21">
+        <v>0.0</v>
+      </c>
+      <c r="D14" s="21" t="n">
         <f>TestCoverage!H16</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="21">
-        <f>C14 + D14</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="20" t="n">
         <f>TestCoverage!B16</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="19">
-        <f>IF($F14=0,1,0)</f>
-        <v>1</v>
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>1.0</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="str">
         <f>TestCoverage!A3 &amp; " (" &amp; TestCoverage!B3 &amp; ")"</f>
-        <v>Validations &amp; Business Rules (25)</v>
-      </c>
-      <c r="B15" s="21">
+        <v>Validations &amp; Business Rules (30)</v>
+      </c>
+      <c r="B15" s="21" t="n">
         <f>TestCoverage!F3</f>
-        <v>0.76</v>
-      </c>
-      <c r="C15" s="21">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="C15" s="21" t="n">
         <f>TestCoverage!G3</f>
-        <v>0.24</v>
-      </c>
-      <c r="D15" s="21">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="D15" s="21" t="n">
         <f>TestCoverage!H3</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="21">
-        <f>C15 + D15</f>
-        <v>0.24</v>
-      </c>
-      <c r="F15" s="20">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <f t="shared" si="0"/>
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="F15" s="20" t="n">
         <f>TestCoverage!B3</f>
-        <v>25</v>
-      </c>
-      <c r="G15" s="19">
-        <f>IF($F15=0,1,0)</f>
-        <v>0</v>
+        <v>30.0</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <f t="shared" si="1"/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="str">
         <f>TestCoverage!A17 &amp; " (" &amp; TestCoverage!B17 &amp; ")"</f>
-        <v>TOTAL (71)</v>
-      </c>
-      <c r="B16" s="21">
+        <v>TOTAL (76)</v>
+      </c>
+      <c r="B16" s="21" t="n">
         <f>TestCoverage!F17</f>
-        <v>0.91549295774647887</v>
-      </c>
-      <c r="C16" s="21">
+        <v>0.9736842105263158</v>
+      </c>
+      <c r="C16" s="21" t="n">
         <f>TestCoverage!G17</f>
-        <v>8.4507042253521125E-2</v>
-      </c>
-      <c r="D16" s="21">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="D16" s="21" t="n">
         <f>TestCoverage!H17</f>
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="E16" s="21"/>
-      <c r="F16" s="20">
+      <c r="F16" s="20" t="n">
         <f>TestCoverage!B17</f>
-        <v>71</v>
-      </c>
-      <c r="G16" s="19">
+        <v>76.0</v>
+      </c>
+      <c r="G16" s="19" t="n">
         <f>COUNTIF(F2:F14,0)/COUNTA(A2:A14)</f>
-        <v>0.53846153846153844</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/TestCoverageDashboard_QA.xlsx
+++ b/src/test/resources/TestCoverageDashboard_QA.xlsx
@@ -3,12 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F99EDB-2C30-4BDD-AF16-39FB360AD3A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85F9470-2A13-493E-8672-FC876370B32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>Functional Area</t>
   </si>
@@ -94,9 +94,6 @@
     <t>RAI Management</t>
   </si>
   <si>
-    <t>SRT Review Workflow</t>
-  </si>
-  <si>
     <t>Workflow &amp; Status Transitions</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
   </si>
   <si>
     <t>Timeline &amp; SLA Management</t>
-  </si>
-  <si>
-    <t>Automation Execution Coverage - OneMAC SMART</t>
   </si>
   <si>
     <t>Chart Label</t>
@@ -147,6 +141,24 @@
   <si>
     <t>Pending Automation %</t>
   </si>
+  <si>
+    <t>Remaining Label</t>
+  </si>
+  <si>
+    <t>Dynamic Chart Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Automation Execution Coverage - OneMAC SMART</t>
+  </si>
+  <si>
+    <t>Blocked label</t>
+  </si>
+  <si>
+    <t>SRT Review</t>
+  </si>
+  <si>
+    <t>03/30/2026 05:50:29 PM</t>
+  </si>
 </sst>
 </file>
 
@@ -155,7 +167,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="166" formatCode="m/d/yyyy h:mm:ss AM/PM"/>
+    <numFmt numFmtId="166" formatCode="mm/dd/yyyy\ hh:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -214,14 +226,14 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="22"/>
       <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
@@ -271,7 +283,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -295,9 +307,61 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -307,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -335,14 +399,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -356,20 +417,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -493,7 +565,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -506,7 +578,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="1">
+              <a:rPr lang="en-US" sz="1800" b="1">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -518,6 +590,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.39527842010073572"/>
+          <c:y val="1.4130488721310935E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -531,7 +611,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -598,13 +678,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -640,50 +720,50 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
+              <c:f>Dashboard_Data!$I$2:$I$15</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>RAI Management (3)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>SRT Review Workflow ()</c:v>
+                  <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>RAI Management (8)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SRT Review (9)</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>Record Lifecycle Management (17)</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>User Access &amp; Permissions (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>Assignment &amp; Routing (8)</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>API End To End ()</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Search &amp; Filters ()</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>Reporting &amp; Data Export ()</c:v>
+                  <c:v>API End To End (0)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
+                  <c:v>Search &amp; Filters (0)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Email Notifications &amp; Alerts ()</c:v>
+                  <c:v>Reporting &amp; Data Export (0)</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Email Notifications &amp; Alerts (0)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>Document Management ()</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (30)</c:v>
+                  <c:v>Document Management (0)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -695,16 +775,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.93548387096774188</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.94117647058823528</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
@@ -713,10 +793,10 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -728,13 +808,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.93333333333333335</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -785,13 +865,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -827,50 +907,50 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
+              <c:f>Dashboard_Data!$I$2:$I$15</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>RAI Management (3)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>SRT Review Workflow ()</c:v>
+                  <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>RAI Management (8)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SRT Review (9)</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>Record Lifecycle Management (17)</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>User Access &amp; Permissions (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>Assignment &amp; Routing (8)</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>API End To End ()</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Search &amp; Filters ()</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>Reporting &amp; Data Export ()</c:v>
+                  <c:v>API End To End (0)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
+                  <c:v>Search &amp; Filters (0)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Email Notifications &amp; Alerts ()</c:v>
+                  <c:v>Reporting &amp; Data Export (0)</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Email Notifications &amp; Alerts (0)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>Document Management ()</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (30)</c:v>
+                  <c:v>Document Management (0)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -882,16 +962,16 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>6.4516129032258063E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.8823529411764705E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
@@ -915,13 +995,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.6666666666666666E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -936,15 +1016,7 @@
           <c:idx val="6"/>
           <c:order val="2"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Dashboard_Data!$D$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Blocked %</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Blocked</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -957,6 +1029,481 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{628B9EA9-89FB-4894-A9E8-3C8B37BDA441}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A0167F32-3FFF-47A0-BFCB-6704E6DECF33}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000012-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C3C54C4E-86EB-471E-9671-F0B4525FEA55}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{74037F13-F8DC-43FE-A8E5-1A928B7E721B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000014-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{D8BD1AB0-5A3C-4BC3-B3BA-B78853611014}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{AE66600F-0B38-4436-B16E-FDA6CA4638B4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000016-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{FA3ED816-DBDB-4EE1-8284-0E9E2820EC6C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{CC9EDF8D-71DA-4DDD-A392-B04CA3780289}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000018-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{FBB9EBE6-C4AC-42E5-BA77-1281A94DE48A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{FF193D4E-D108-4B10-A1AD-076168A071C5}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001A-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{AFB06330-DA14-467E-B6D3-790F4A9EFE73}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001B-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{3FB840F3-5776-4A58-B6E1-94E4486DECF9}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001C-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{25712B00-6464-49F4-81F8-C2F81842EC5E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001D-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{E28DAB9D-684C-45EC-930F-DD9C7C18A483}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001E-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
             <c:spPr>
               <a:noFill/>
@@ -972,13 +1519,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -986,7 +1533,7 @@
             </c:txPr>
             <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
@@ -994,6 +1541,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1014,50 +1562,50 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
+              <c:f>Dashboard_Data!$I$2:$I$15</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>RAI Management (3)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>SRT Review Workflow ()</c:v>
+                  <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>RAI Management (8)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SRT Review (9)</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>Record Lifecycle Management (17)</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>User Access &amp; Permissions (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>Assignment &amp; Routing (8)</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>API End To End ()</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Search &amp; Filters ()</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>Reporting &amp; Data Export ()</c:v>
+                  <c:v>API End To End (0)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
+                  <c:v>Search &amp; Filters (0)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Email Notifications &amp; Alerts ()</c:v>
+                  <c:v>Reporting &amp; Data Export (0)</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Email Notifications &amp; Alerts (0)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>Document Management ()</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (30)</c:v>
+                  <c:v>Document Management (0)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1114,6 +1662,14 @@
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>Dashboard_Data!$J$2:$J$15</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="14"/>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-FB6E-45FE-8991-B3D9A8DE49D8}"/>
             </c:ext>
@@ -1123,15 +1679,7 @@
           <c:idx val="0"/>
           <c:order val="3"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Dashboard_Data!$G$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Pending Automation %</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Not Automated</c:v>
           </c:tx>
           <c:spPr>
             <a:solidFill>
@@ -1146,7 +1694,481 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
-            <c:numFmt formatCode="0%;\-0%;&quot;&quot;" sourceLinked="0"/>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C45FE45E-6C3C-4BA7-A8CC-3517844F29B5}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F1265293-6260-4E48-9B2B-9A05B8DFE475}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DFEDAE41-B3B4-49A0-8B60-48AFE6A3BF6A}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{17EB1791-0AFB-4F8E-85C3-A99607CE31E8}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{06DD9118-998E-4E52-AB95-D0055FBE08EC}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DA365F32-443F-439C-901F-3B90D01E05B2}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DFA2C739-7E00-4569-89D9-038696E30C18}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{20AE6C04-3B74-4C31-B475-10F35842C548}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DB60A831-B2E9-49A9-A145-8DFDC78443C6}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{A21B692F-5060-4905-9EDE-A5C9939029F8}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{38271A87-C9BC-4937-9DCF-AD30AD97B06E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F3C3B93A-6402-415F-B72B-8310DFC3EC1E}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{489F7521-4FF1-4ECC-B830-A2E7D3D3C9AD}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{7090F557-D22A-4F3B-B8DD-D81313A742D7}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="ctr"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000010-0828-4F43-8022-2CA88E3DA78C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:spPr>
               <a:noFill/>
               <a:ln>
@@ -1161,13 +2183,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -1175,7 +2197,7 @@
             </c:txPr>
             <c:dLblPos val="ctr"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
@@ -1183,6 +2205,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1203,50 +2226,50 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Dashboard_Data!$A$2:$A$15</c:f>
+              <c:f>Dashboard_Data!$I$2:$I$15</c:f>
               <c:strCache>
                 <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>RAI Management (3)</c:v>
+                  <c:v>⚠️ Accessibility (Section 508 Compliance) (1)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>SRT Review Workflow ()</c:v>
+                  <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>RAI Management (8)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>SRT Review (9)</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Workflow &amp; Status Transitions (7)</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>Record Lifecycle Management (17)</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>User Access &amp; Permissions (1)</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>User Access &amp; Permissions (7)</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>Assignment &amp; Routing (8)</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>API End To End ()</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Search &amp; Filters ()</c:v>
-                </c:pt>
                 <c:pt idx="8">
-                  <c:v>Reporting &amp; Data Export ()</c:v>
+                  <c:v>API End To End (0)</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>Accessibility (Section 508 Compliance) ()</c:v>
+                  <c:v>Search &amp; Filters (0)</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Email Notifications &amp; Alerts ()</c:v>
+                  <c:v>Reporting &amp; Data Export (0)</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Email Notifications &amp; Alerts (0)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Timeline &amp; SLA Management (10)</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>Document Management ()</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>Validations &amp; Business Rules (30)</c:v>
+                  <c:v>Document Management (0)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1261,7 +2284,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -1276,10 +2299,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1</c:v>
@@ -1291,18 +2314,41 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>Dashboard_Data!$H$2:$H$15</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="14"/>
+                  <c:pt idx="8">
+                    <c:v>Not Automated</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Not Automated</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Not Automated</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Not Automated</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Not Automated</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000001-29EC-408F-AD2C-7EC024EDF909}"/>
             </c:ext>
@@ -1317,7 +2363,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="30"/>
+        <c:gapWidth val="12"/>
         <c:overlap val="100"/>
         <c:axId val="974676704"/>
         <c:axId val="974680544"/>
@@ -1351,7 +2397,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
@@ -1425,9 +2471,9 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.46588824688972519"/>
-          <c:y val="0.9143754541065745"/>
-          <c:w val="0.30556385581748019"/>
+          <c:x val="0.33472849566582685"/>
+          <c:y val="0.92002766460406049"/>
+          <c:w val="0.51387630993906852"/>
           <c:h val="7.9481106747818109E-2"/>
         </c:manualLayout>
       </c:layout>
@@ -1444,13 +2490,13 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1200" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2050,16 +3096,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>209000</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>144431</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28025</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>20606</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>227134</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>66260</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>398584</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>132935</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2409,30 +3455,31 @@
   <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="32.5703125"/>
-    <col min="2" max="2" customWidth="true" width="24.0"/>
-    <col min="3" max="3" customWidth="true" width="24.5703125"/>
-    <col min="4" max="4" customWidth="true" width="14.7109375"/>
-    <col min="5" max="5" customWidth="true" width="9.140625"/>
-    <col min="6" max="6" customWidth="true" width="8.140625"/>
-    <col min="7" max="7" customWidth="true" width="7.140625"/>
-    <col min="8" max="8" customWidth="true" width="11.28515625"/>
-    <col min="9" max="9" customWidth="true" width="24.0"/>
+    <col min="1" max="1" width="34.7109375" customWidth="1"/>
+    <col min="2" max="3" width="24.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="27" t="n">
-        <v>46105.66914611111</v>
-      </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="A1" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="26">
+        <v>46111.738459328706</v>
+      </c>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
@@ -2464,201 +3511,209 @@
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="9" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="C3" s="9" t="n">
-        <v>28.0</v>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="7" t="n">
+      <c r="B3" s="9">
+        <v>31</v>
+      </c>
+      <c r="C3" s="9">
+        <v>29</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2</v>
+      </c>
+      <c r="E3" s="9">
+        <v>0</v>
+      </c>
+      <c r="F3" s="7">
         <f>IF(B3=0,"",C3/B3)</f>
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="G3" s="7" t="n">
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="G3" s="7">
         <f>IFERROR(D3/B3,0)</f>
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="H3" s="7" t="n">
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="H3" s="7">
         <f>IFERROR(E3/B3,0)</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="10" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="7" t="n">
+      <c r="B4" s="10">
+        <v>8</v>
+      </c>
+      <c r="C4" s="10">
+        <v>8</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0</v>
+      </c>
+      <c r="F4" s="7">
         <f t="shared" ref="F4:F16" si="0">IF(B4=0,"",C4/B4)</f>
-        <v>1.0</v>
-      </c>
-      <c r="G4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7">
         <f t="shared" ref="G4:G14" si="1">IFERROR(D4/B4,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7">
         <f t="shared" ref="H4:H14" si="2">IFERROR(E4/B4,0)</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="7" t="str">
+        <v>37</v>
+      </c>
+      <c r="B5" s="9">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9">
+        <v>9</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0</v>
+      </c>
+      <c r="F5" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B6" s="10">
+        <v>7</v>
+      </c>
+      <c r="C6" s="10">
+        <v>7</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="9" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>17.0</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" s="9">
+        <v>17</v>
+      </c>
+      <c r="C7" s="9">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="7" t="n">
+      <c r="B8" s="9">
+        <v>7</v>
+      </c>
+      <c r="C8" s="10">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" s="9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9">
+        <v>8</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="9"/>
       <c r="C10" s="10"/>
@@ -2668,19 +3723,19 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
@@ -2690,19 +3745,19 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
@@ -2712,41 +3767,49 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" s="1" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="7" t="str">
+        <v>29</v>
+      </c>
+      <c r="B13" s="9">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="9"/>
       <c r="C14" s="10"/>
@@ -2756,48 +3819,48 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="7">
         <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-      <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7">
         <f t="shared" si="2"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="9" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="C15" s="9" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="D15" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F15" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" s="9">
+        <v>10</v>
+      </c>
+      <c r="C15" s="9">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7">
         <f t="shared" si="0"/>
-        <v>1.0</v>
-      </c>
-      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="7">
         <f>IFERROR(D15/B15,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7">
         <f t="shared" ref="H15:H17" si="3">IFERROR(E15/B15,0)</f>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" s="9"/>
       <c r="C16" s="10"/>
@@ -2807,51 +3870,51 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="7">
         <f>IFERROR(D16/B16,0)</f>
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7">
         <f t="shared" si="3"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="14">
         <f>SUM(B3:B16)</f>
-        <v>76.0</v>
-      </c>
-      <c r="C17" s="15" t="n">
+        <v>98</v>
+      </c>
+      <c r="C17" s="14">
         <f>SUM(C3:C15)</f>
-        <v>74.0</v>
-      </c>
-      <c r="D17" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="D17" s="14">
         <f>SUM(D3:D15)</f>
-        <v>2.0</v>
-      </c>
-      <c r="E17" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="14">
         <f>SUM(E3:E15)</f>
-        <v>0.0</v>
-      </c>
-      <c r="F17" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="15">
         <f t="shared" ref="F17" si="4">IFERROR(C17/B17,0)</f>
-        <v>0.9736842105263158</v>
-      </c>
-      <c r="G17" s="16" t="n">
+        <v>0.96938775510204078</v>
+      </c>
+      <c r="G17" s="15">
         <f t="shared" ref="G17" si="5">IFERROR(D17/B17,0)</f>
-        <v>0.02631578947368421</v>
-      </c>
-      <c r="H17" s="16" t="n">
+        <v>3.0612244897959183E-2</v>
+      </c>
+      <c r="H17" s="15">
         <f t="shared" si="3"/>
-        <v>0.0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="B1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F3:F16">
@@ -2888,168 +3951,156 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8733FBF-1B6F-4496-80CB-20AA79BD08C8}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="14.7109375"/>
-    <col min="2" max="2" customWidth="true" width="23.5703125"/>
-    <col min="5" max="5" customWidth="true" width="18.0"/>
-    <col min="6" max="6" customWidth="true" width="25.7109375"/>
-    <col min="7" max="7" customWidth="true" width="15.140625"/>
-    <col min="8" max="8" customWidth="true" width="10.5703125"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" customWidth="1"/>
+    <col min="8" max="8" width="49.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="30.75" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
+    <row r="1" spans="1:16" ht="33" x14ac:dyDescent="0.25">
+      <c r="E1" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
     </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <f>TestCoverage!C1</f>
-        <v>46105.66914611111</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
+    <row r="3" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="18" t="n">
-        <f>TestCoverage!B17</f>
-        <v>76.0</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="5" t="str">
+        <f>TestCoverage!B1</f>
+        <v>03/30/2026 05:50:29 PM</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="18" t="n">
-        <f>TestCoverage!C17</f>
-        <v>74.0</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="17">
+        <f>TestCoverage!B17</f>
+        <v>98</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <f>TestCoverage!D17</f>
-        <v>2.0</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="G5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="17">
+        <f>TestCoverage!C17</f>
+        <v>95</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <f>TestCoverage!E17</f>
-        <v>0.0</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="G6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="17">
+        <f>TestCoverage!D17</f>
+        <v>3</v>
+      </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+    <row r="7" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="17" t="n">
-        <f>IFERROR(F4/F3,"")</f>
-        <v>0.9736842105263158</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="G7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="17">
+        <f>TestCoverage!E17</f>
+        <v>0</v>
+      </c>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
+    <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="G8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="16">
+        <f>IFERROR(H5/H4,"")</f>
+        <v>0.96938775510204078</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E1:P1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:F5">
+  <conditionalFormatting sqref="G6:H6">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>$F$5&gt;0</formula>
+      <formula>$H$6&gt;0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="5" priority="2">
-      <formula>$F$5=0</formula>
+      <formula>$H$6=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E6:F6">
+  <conditionalFormatting sqref="G7:H7">
     <cfRule type="expression" dxfId="4" priority="3">
-      <formula>$F$6&gt;0</formula>
+      <formula>$H$7&gt;0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$F$6=0</formula>
+      <formula>$H$7=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E7:F7">
+  <conditionalFormatting sqref="G8:H8">
     <cfRule type="cellIs" dxfId="2" priority="5" operator="lessThan">
       <formula>0.6</formula>
     </cfRule>
@@ -3069,19 +4120,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC817E08-797F-444D-BF6E-D4C8FC527215}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.85546875"/>
-    <col min="2" max="2" customWidth="true" width="14.0"/>
-    <col min="4" max="5" customWidth="true" width="13.85546875"/>
-    <col min="6" max="6" customWidth="true" width="10.42578125"/>
-    <col min="7" max="7" customWidth="true" width="26.140625"/>
+    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="4" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" customWidth="1"/>
+    <col min="9" max="9" width="39.140625" customWidth="1"/>
+    <col min="10" max="10" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B1" s="22" t="s">
         <v>4</v>
@@ -3093,465 +4147,645 @@
         <v>6</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" t="s">
         <v>34</v>
       </c>
+      <c r="J1" s="24" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="str">
-        <f>TestCoverage!A4 &amp; " (" &amp; TestCoverage!B4 &amp; ")"</f>
-        <v>RAI Management (3)</v>
-      </c>
-      <c r="B2" s="21" t="n">
+    <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="str">
+        <f>TestCoverage!A13 &amp; " (" &amp; IFERROR(TestCoverage!B13+0,0) &amp; ")"</f>
+        <v>Accessibility (Section 508 Compliance) (1)</v>
+      </c>
+      <c r="B2" s="20">
+        <f>TestCoverage!F13</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="20">
+        <f>TestCoverage!G13</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="20">
+        <f>TestCoverage!H13</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="20">
+        <f>C2 + D2</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="19">
+        <f>TestCoverage!B13</f>
+        <v>1</v>
+      </c>
+      <c r="G2" s="18">
+        <f>IF($F2=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="19" t="str">
+        <f>IF(G2=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I2" s="19" t="str">
+        <f>IF(AND(C2&gt;0,F2&gt;0),"⚠️ "&amp;A2,A2)</f>
+        <v>⚠️ Accessibility (Section 508 Compliance) (1)</v>
+      </c>
+      <c r="J2" s="19" t="str">
+        <f>IF(D2=100%,"Blocked","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="str">
+        <f>TestCoverage!A3 &amp; " (" &amp; IFERROR(TestCoverage!B3+0,0) &amp; ")"</f>
+        <v>Validations &amp; Business Rules (31)</v>
+      </c>
+      <c r="B3" s="20">
+        <f>TestCoverage!F3</f>
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="C3" s="20">
+        <f>TestCoverage!G3</f>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="D3" s="20">
+        <f>TestCoverage!H3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="20">
+        <f>C3 + D3</f>
+        <v>6.4516129032258063E-2</v>
+      </c>
+      <c r="F3" s="19">
+        <f>TestCoverage!B3</f>
+        <v>31</v>
+      </c>
+      <c r="G3" s="18">
+        <f>IF($F3=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="19" t="str">
+        <f>IF(G3=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I3" s="19" t="str">
+        <f>IF(AND(C3&gt;0,F3&gt;0),"⚠️ "&amp;A3,A3)</f>
+        <v>⚠️ Validations &amp; Business Rules (31)</v>
+      </c>
+      <c r="J3" s="19" t="str">
+        <f>IF(D3=100%,"Blocked","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="str">
+        <f>TestCoverage!A4 &amp; " (" &amp; IFERROR(TestCoverage!B4+0,0) &amp; ")"</f>
+        <v>RAI Management (8)</v>
+      </c>
+      <c r="B4" s="20">
         <f>TestCoverage!F4</f>
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20">
         <f>TestCoverage!G4</f>
-        <v>0.0</v>
-      </c>
-      <c r="D2" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="20">
         <f>TestCoverage!H4</f>
-        <v>0.0</v>
-      </c>
-      <c r="E2" s="21" t="n">
-        <f t="shared" ref="E2:E15" si="0">C2 + D2</f>
-        <v>0.0</v>
-      </c>
-      <c r="F2" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="20">
+        <f>C4 + D4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="19">
         <f>TestCoverage!B4</f>
-        <v>3.0</v>
-      </c>
-      <c r="G2" s="19" t="n">
-        <f t="shared" ref="G2:G15" si="1">IF($F2=0,1,0)</f>
-        <v>0.0</v>
+        <v>8</v>
+      </c>
+      <c r="G4" s="18">
+        <f>IF($F4=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="19" t="str">
+        <f>IF(G4=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I4" s="19" t="str">
+        <f>IF(AND(C4&gt;0,F4&gt;0),"⚠️ "&amp;A4,A4)</f>
+        <v>RAI Management (8)</v>
+      </c>
+      <c r="J4" s="19" t="str">
+        <f>IF(D4=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="str">
-        <f>TestCoverage!A5 &amp; " (" &amp; TestCoverage!B5 &amp; ")"</f>
-        <v>SRT Review Workflow ()</v>
-      </c>
-      <c r="B3" s="21" t="str">
+    <row r="5" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="str">
+        <f>TestCoverage!A5 &amp; " (" &amp; IFERROR(TestCoverage!B5+0,0) &amp; ")"</f>
+        <v>SRT Review (9)</v>
+      </c>
+      <c r="B5" s="20">
         <f>TestCoverage!F5</f>
+        <v>1</v>
+      </c>
+      <c r="C5" s="20">
+        <f>TestCoverage!G5</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="20">
+        <f>TestCoverage!H5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="20">
+        <f>C5 + D5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="19">
+        <f>TestCoverage!B5</f>
+        <v>9</v>
+      </c>
+      <c r="G5" s="18">
+        <f>IF($F5=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="19" t="str">
+        <f>IF(G5=100%,"Not Automated","")</f>
         <v/>
       </c>
-      <c r="C3" s="21" t="n">
-        <f>TestCoverage!G5</f>
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="21" t="n">
-        <f>TestCoverage!H5</f>
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="20" t="n">
-        <f>TestCoverage!B5</f>
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>1.0</v>
+      <c r="I5" s="19" t="str">
+        <f>IF(AND(C5&gt;0,F5&gt;0),"⚠️ "&amp;A5,A5)</f>
+        <v>SRT Review (9)</v>
+      </c>
+      <c r="J5" s="19" t="str">
+        <f>IF(D5=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="str">
-        <f>TestCoverage!A6 &amp; " (" &amp; TestCoverage!B6 &amp; ")"</f>
+    <row r="6" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="str">
+        <f>TestCoverage!A6 &amp; " (" &amp; IFERROR(TestCoverage!B6+0,0) &amp; ")"</f>
         <v>Workflow &amp; Status Transitions (7)</v>
       </c>
-      <c r="B4" s="21" t="n">
+      <c r="B6" s="20">
         <f>TestCoverage!F6</f>
-        <v>1.0</v>
-      </c>
-      <c r="C4" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="20">
         <f>TestCoverage!G6</f>
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="20">
         <f>TestCoverage!H6</f>
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="20">
+        <f>C6 + D6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="19">
         <f>TestCoverage!B6</f>
-        <v>7.0</v>
-      </c>
-      <c r="G4" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
+        <v>7</v>
+      </c>
+      <c r="G6" s="18">
+        <f>IF($F6=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="19" t="str">
+        <f>IF(G6=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I6" s="19" t="str">
+        <f>IF(AND(C6&gt;0,F6&gt;0),"⚠️ "&amp;A6,A6)</f>
+        <v>Workflow &amp; Status Transitions (7)</v>
+      </c>
+      <c r="J6" s="19" t="str">
+        <f>IF(D6=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="str">
-        <f>TestCoverage!A7 &amp; " (" &amp; TestCoverage!B7 &amp; ")"</f>
+    <row r="7" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="str">
+        <f>TestCoverage!A7 &amp; " (" &amp; IFERROR(TestCoverage!B7+0,0) &amp; ")"</f>
         <v>Record Lifecycle Management (17)</v>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B7" s="20">
         <f>TestCoverage!F7</f>
-        <v>1.0</v>
-      </c>
-      <c r="C5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="20">
         <f>TestCoverage!G7</f>
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="20">
         <f>TestCoverage!H7</f>
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="20">
+        <f>C7 + D7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="19">
         <f>TestCoverage!B7</f>
-        <v>17.0</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
+        <v>17</v>
+      </c>
+      <c r="G7" s="18">
+        <f>IF($F7=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="19" t="str">
+        <f>IF(G7=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I7" s="19" t="str">
+        <f>IF(AND(C7&gt;0,F7&gt;0),"⚠️ "&amp;A7,A7)</f>
+        <v>Record Lifecycle Management (17)</v>
+      </c>
+      <c r="J7" s="19" t="str">
+        <f>IF(D7=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="str">
-        <f>TestCoverage!A8 &amp; " (" &amp; TestCoverage!B8 &amp; ")"</f>
-        <v>User Access &amp; Permissions (1)</v>
-      </c>
-      <c r="B6" s="21" t="n">
+    <row r="8" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="str">
+        <f>TestCoverage!A8 &amp; " (" &amp; IFERROR(TestCoverage!B8+0,0) &amp; ")"</f>
+        <v>User Access &amp; Permissions (7)</v>
+      </c>
+      <c r="B8" s="20">
         <f>TestCoverage!F8</f>
-        <v>1.0</v>
-      </c>
-      <c r="C6" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="20">
         <f>TestCoverage!G8</f>
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="20">
         <f>TestCoverage!H8</f>
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="20">
+        <f>C8 + D8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="19">
         <f>TestCoverage!B8</f>
-        <v>1.0</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
+        <v>7</v>
+      </c>
+      <c r="G8" s="18">
+        <f>IF($F8=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="19" t="str">
+        <f>IF(G8=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I8" s="19" t="str">
+        <f>IF(AND(C8&gt;0,F8&gt;0),"⚠️ "&amp;A8,A8)</f>
+        <v>User Access &amp; Permissions (7)</v>
+      </c>
+      <c r="J8" s="19" t="str">
+        <f>IF(D8=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="str">
-        <f>TestCoverage!A9 &amp; " (" &amp; TestCoverage!B9 &amp; ")"</f>
+    <row r="9" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="str">
+        <f>TestCoverage!A9 &amp; " (" &amp; IFERROR(TestCoverage!B9+0,0) &amp; ")"</f>
         <v>Assignment &amp; Routing (8)</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B9" s="20">
         <f>TestCoverage!F9</f>
-        <v>1.0</v>
-      </c>
-      <c r="C7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="20">
         <f>TestCoverage!G9</f>
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20">
         <f>TestCoverage!H9</f>
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="20">
+        <f>C9 + D9</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="19">
         <f>TestCoverage!B9</f>
-        <v>8.0</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
+        <v>8</v>
+      </c>
+      <c r="G9" s="18">
+        <f>IF($F9=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="19" t="str">
+        <f>IF(G9=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I9" s="19" t="str">
+        <f>IF(AND(C9&gt;0,F9&gt;0),"⚠️ "&amp;A9,A9)</f>
+        <v>Assignment &amp; Routing (8)</v>
+      </c>
+      <c r="J9" s="19" t="str">
+        <f>IF(D9=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="str">
-        <f>TestCoverage!A10 &amp; " (" &amp; TestCoverage!B10 &amp; ")"</f>
-        <v>API End To End ()</v>
-      </c>
-      <c r="B8" s="21" t="str">
+    <row r="10" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="str">
+        <f>TestCoverage!A10 &amp; " (" &amp; IFERROR(TestCoverage!B10+0,0) &amp; ")"</f>
+        <v>API End To End (0)</v>
+      </c>
+      <c r="B10" s="20" t="str">
         <f>TestCoverage!F10</f>
         <v/>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C10" s="20">
         <f>TestCoverage!G10</f>
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="20">
         <f>TestCoverage!H10</f>
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20">
+        <f>C10 + D10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="19">
         <f>TestCoverage!B10</f>
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <f>IF($F10=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H10" s="19" t="str">
+        <f>IF(G10=100%,"Not Automated","")</f>
+        <v>Not Automated</v>
+      </c>
+      <c r="I10" s="19" t="str">
+        <f>IF(AND(C10&gt;0,F10&gt;0),"⚠️ "&amp;A10,A10)</f>
+        <v>API End To End (0)</v>
+      </c>
+      <c r="J10" s="19" t="str">
+        <f>IF(D10=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="str">
-        <f>TestCoverage!A11 &amp; " (" &amp; TestCoverage!B11 &amp; ")"</f>
-        <v>Search &amp; Filters ()</v>
-      </c>
-      <c r="B9" s="21" t="str">
+    <row r="11" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="str">
+        <f>TestCoverage!A11 &amp; " (" &amp; IFERROR(TestCoverage!B11+0,0) &amp; ")"</f>
+        <v>Search &amp; Filters (0)</v>
+      </c>
+      <c r="B11" s="20" t="str">
         <f>TestCoverage!F11</f>
         <v/>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C11" s="20">
         <f>TestCoverage!G11</f>
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="20">
         <f>TestCoverage!H11</f>
-        <v>0.0</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
+        <f>C11 + D11</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="19">
         <f>TestCoverage!B11</f>
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <f>IF($F11=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H11" s="19" t="str">
+        <f>IF(G11=100%,"Not Automated","")</f>
+        <v>Not Automated</v>
+      </c>
+      <c r="I11" s="19" t="str">
+        <f>IF(AND(C11&gt;0,F11&gt;0),"⚠️ "&amp;A11,A11)</f>
+        <v>Search &amp; Filters (0)</v>
+      </c>
+      <c r="J11" s="19" t="str">
+        <f>IF(D11=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="str">
-        <f>TestCoverage!A12 &amp; " (" &amp; TestCoverage!B12 &amp; ")"</f>
-        <v>Reporting &amp; Data Export ()</v>
-      </c>
-      <c r="B10" s="21" t="str">
+    <row r="12" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="str">
+        <f>TestCoverage!A12 &amp; " (" &amp; IFERROR(TestCoverage!B12+0,0) &amp; ")"</f>
+        <v>Reporting &amp; Data Export (0)</v>
+      </c>
+      <c r="B12" s="20" t="str">
         <f>TestCoverage!F12</f>
         <v/>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C12" s="20">
         <f>TestCoverage!G12</f>
-        <v>0.0</v>
-      </c>
-      <c r="D10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="20">
         <f>TestCoverage!H12</f>
-        <v>0.0</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="20">
+        <f>C12 + D12</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="19">
         <f>TestCoverage!B12</f>
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <f>IF($F12=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="19" t="str">
+        <f>IF(G12=100%,"Not Automated","")</f>
+        <v>Not Automated</v>
+      </c>
+      <c r="I12" s="19" t="str">
+        <f>IF(AND(C12&gt;0,F12&gt;0),"⚠️ "&amp;A12,A12)</f>
+        <v>Reporting &amp; Data Export (0)</v>
+      </c>
+      <c r="J12" s="19" t="str">
+        <f>IF(D12=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="str">
-        <f>TestCoverage!A13 &amp; " (" &amp; TestCoverage!B13 &amp; ")"</f>
-        <v>Accessibility (Section 508 Compliance) ()</v>
-      </c>
-      <c r="B11" s="21" t="str">
-        <f>TestCoverage!F13</f>
-        <v/>
-      </c>
-      <c r="C11" s="21" t="n">
-        <f>TestCoverage!G13</f>
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <f>TestCoverage!H13</f>
-        <v>0.0</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <f>TestCoverage!B13</f>
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="str">
-        <f>TestCoverage!A14 &amp; " (" &amp; TestCoverage!B14 &amp; ")"</f>
-        <v>Email Notifications &amp; Alerts ()</v>
-      </c>
-      <c r="B12" s="21" t="str">
+    <row r="13" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="str">
+        <f>TestCoverage!A14 &amp; " (" &amp; IFERROR(TestCoverage!B14+0,0) &amp; ")"</f>
+        <v>Email Notifications &amp; Alerts (0)</v>
+      </c>
+      <c r="B13" s="20" t="str">
         <f>TestCoverage!F14</f>
         <v/>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C13" s="20">
         <f>TestCoverage!G14</f>
-        <v>0.0</v>
-      </c>
-      <c r="D12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="20">
         <f>TestCoverage!H14</f>
-        <v>0.0</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <f>C13 + D13</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="19">
         <f>TestCoverage!B14</f>
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <f>IF($F13=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="19" t="str">
+        <f>IF(G13=100%,"Not Automated","")</f>
+        <v>Not Automated</v>
+      </c>
+      <c r="I13" s="19" t="str">
+        <f>IF(AND(C13&gt;0,F13&gt;0),"⚠️ "&amp;A13,A13)</f>
+        <v>Email Notifications &amp; Alerts (0)</v>
+      </c>
+      <c r="J13" s="19" t="str">
+        <f>IF(D13=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="str">
-        <f>TestCoverage!A15 &amp; " (" &amp; TestCoverage!B15 &amp; ")"</f>
+    <row r="14" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="str">
+        <f>TestCoverage!A15 &amp; " (" &amp; IFERROR(TestCoverage!B15+0,0) &amp; ")"</f>
         <v>Timeline &amp; SLA Management (10)</v>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B14" s="20">
         <f>TestCoverage!F15</f>
-        <v>1.0</v>
-      </c>
-      <c r="C13" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="20">
         <f>TestCoverage!G15</f>
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="20">
         <f>TestCoverage!H15</f>
-        <v>0.0</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="20">
+        <f>C14 + D14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="19">
         <f>TestCoverage!B15</f>
-        <v>10.0</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
+        <v>10</v>
+      </c>
+      <c r="G14" s="18">
+        <f>IF($F14=0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="19" t="str">
+        <f>IF(G14=100%,"Not Automated","")</f>
+        <v/>
+      </c>
+      <c r="I14" s="19" t="str">
+        <f>IF(AND(C14&gt;0,F14&gt;0),"⚠️ "&amp;A14,A14)</f>
+        <v>Timeline &amp; SLA Management (10)</v>
+      </c>
+      <c r="J14" s="19" t="str">
+        <f>IF(D14=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="str">
-        <f>TestCoverage!A16 &amp; " (" &amp; TestCoverage!B16 &amp; ")"</f>
-        <v>Document Management ()</v>
-      </c>
-      <c r="B14" s="21" t="str">
+    <row r="15" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="str">
+        <f>TestCoverage!A16 &amp; " (" &amp; IFERROR(TestCoverage!B16+0,0) &amp; ")"</f>
+        <v>Document Management (0)</v>
+      </c>
+      <c r="B15" s="20" t="str">
         <f>TestCoverage!F16</f>
         <v/>
       </c>
-      <c r="C14" s="21" t="n">
+      <c r="C15" s="20">
         <f>TestCoverage!G16</f>
-        <v>0.0</v>
-      </c>
-      <c r="D14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="20">
         <f>TestCoverage!H16</f>
-        <v>0.0</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.0</v>
-      </c>
-      <c r="F14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="20">
+        <f>C15 + D15</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="19">
         <f>TestCoverage!B16</f>
-        <v>0.0</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>1.0</v>
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
+        <f>IF($F15=0,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="19" t="str">
+        <f>IF(G15=100%,"Not Automated","")</f>
+        <v>Not Automated</v>
+      </c>
+      <c r="I15" s="19" t="str">
+        <f>IF(AND(C15&gt;0,F15&gt;0),"⚠️ "&amp;A15,A15)</f>
+        <v>Document Management (0)</v>
+      </c>
+      <c r="J15" s="19" t="str">
+        <f>IF(D15=100%,"Blocked","")</f>
+        <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="str">
-        <f>TestCoverage!A3 &amp; " (" &amp; TestCoverage!B3 &amp; ")"</f>
-        <v>Validations &amp; Business Rules (30)</v>
-      </c>
-      <c r="B15" s="21" t="n">
-        <f>TestCoverage!F3</f>
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="C15" s="21" t="n">
-        <f>TestCoverage!G3</f>
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <f>TestCoverage!H3</f>
-        <v>0.0</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <f t="shared" si="0"/>
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="F15" s="20" t="n">
-        <f>TestCoverage!B3</f>
-        <v>30.0</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <f t="shared" si="1"/>
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="str">
+    <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="str">
         <f>TestCoverage!A17 &amp; " (" &amp; TestCoverage!B17 &amp; ")"</f>
-        <v>TOTAL (76)</v>
-      </c>
-      <c r="B16" s="21" t="n">
+        <v>TOTAL (98)</v>
+      </c>
+      <c r="B16" s="20">
         <f>TestCoverage!F17</f>
-        <v>0.9736842105263158</v>
-      </c>
-      <c r="C16" s="21" t="n">
+        <v>0.96938775510204078</v>
+      </c>
+      <c r="C16" s="20">
         <f>TestCoverage!G17</f>
-        <v>0.02631578947368421</v>
-      </c>
-      <c r="D16" s="21" t="n">
+        <v>3.0612244897959183E-2</v>
+      </c>
+      <c r="D16" s="20">
         <f>TestCoverage!H17</f>
-        <v>0.0</v>
-      </c>
-      <c r="E16" s="21"/>
-      <c r="F16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="19">
         <f>TestCoverage!B17</f>
-        <v>76.0</v>
-      </c>
-      <c r="G16" s="19" t="n">
+        <v>98</v>
+      </c>
+      <c r="G16" s="18">
         <f>COUNTIF(F2:F14,0)/COUNTA(A2:A14)</f>
-        <v>0.5384615384615384</v>
-      </c>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G16">
-    <sortCondition ref="E2:E16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J16">
+    <sortCondition descending="1" ref="E2:E16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/TestCoverageDashboard_QA.xlsx
+++ b/src/test/resources/TestCoverageDashboard_QA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\57901\smart-test-automation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85F9470-2A13-493E-8672-FC876370B32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C3BE40-A442-4216-90C8-6273E372EA3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{79FC711E-34A0-4D45-A805-C86E1CFB22CF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestCoverage" sheetId="1" r:id="rId1"/>
@@ -730,7 +730,7 @@
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SRT Review (9)</c:v>
@@ -781,7 +781,7 @@
                   <c:v>0.93548387096774188</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -917,7 +917,7 @@
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SRT Review (9)</c:v>
@@ -1036,7 +1036,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{628B9EA9-89FB-4894-A9E8-3C8B37BDA441}" type="CELLRANGE">
+                    <a:fld id="{7E971F8A-D4C1-4A67-B849-67866DF5C320}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1069,7 +1069,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A0167F32-3FFF-47A0-BFCB-6704E6DECF33}" type="CELLRANGE">
+                    <a:fld id="{52FD84B8-5320-4AB5-8E6E-D02611B5E039}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1103,7 +1103,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C3C54C4E-86EB-471E-9671-F0B4525FEA55}" type="CELLRANGE">
+                    <a:fld id="{4C2B9484-F3A1-4A8D-A074-AA3503AF4296}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1137,7 +1137,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74037F13-F8DC-43FE-A8E5-1A928B7E721B}" type="CELLRANGE">
+                    <a:fld id="{393DC6C6-9314-492F-A296-17A4B029839E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1171,7 +1171,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D8BD1AB0-5A3C-4BC3-B3BA-B78853611014}" type="CELLRANGE">
+                    <a:fld id="{46F207B5-4528-4E94-98B0-723755E3484B}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1205,7 +1205,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AE66600F-0B38-4436-B16E-FDA6CA4638B4}" type="CELLRANGE">
+                    <a:fld id="{A4806C86-B768-4356-B97E-88020BD47DA5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1239,7 +1239,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FA3ED816-DBDB-4EE1-8284-0E9E2820EC6C}" type="CELLRANGE">
+                    <a:fld id="{CD864383-827D-4B65-917F-50FC702E57B8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1273,7 +1273,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{CC9EDF8D-71DA-4DDD-A392-B04CA3780289}" type="CELLRANGE">
+                    <a:fld id="{E228761B-798D-4E65-B089-3EE44059070F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1307,7 +1307,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FBB9EBE6-C4AC-42E5-BA77-1281A94DE48A}" type="CELLRANGE">
+                    <a:fld id="{643AF244-156B-4522-80F7-6A9C7214C852}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1341,7 +1341,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FF193D4E-D108-4B10-A1AD-076168A071C5}" type="CELLRANGE">
+                    <a:fld id="{1B4AD456-3D80-48FC-B06A-40B5FBBE845E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1375,7 +1375,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AFB06330-DA14-467E-B6D3-790F4A9EFE73}" type="CELLRANGE">
+                    <a:fld id="{69A71DAA-C3DA-468B-BDEA-E25243530173}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1409,7 +1409,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{3FB840F3-5776-4A58-B6E1-94E4486DECF9}" type="CELLRANGE">
+                    <a:fld id="{E0659EEA-7871-4F05-9593-58CE3E243651}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1443,7 +1443,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{25712B00-6464-49F4-81F8-C2F81842EC5E}" type="CELLRANGE">
+                    <a:fld id="{BB67D1EE-E5BD-484F-988F-B640E972AFB4}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1477,7 +1477,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E28DAB9D-684C-45EC-930F-DD9C7C18A483}" type="CELLRANGE">
+                    <a:fld id="{9E49724E-FF95-4F89-A66F-BACF5A61BC52}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1572,7 +1572,7 @@
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SRT Review (9)</c:v>
@@ -1701,7 +1701,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C45FE45E-6C3C-4BA7-A8CC-3517844F29B5}" type="CELLRANGE">
+                    <a:fld id="{703A39A3-E75B-4534-9A7E-AEAC6EC01CED}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1734,7 +1734,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F1265293-6260-4E48-9B2B-9A05B8DFE475}" type="CELLRANGE">
+                    <a:fld id="{7F373AF3-B0B4-4458-A2F9-FF9093DBCD4E}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1768,7 +1768,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DFEDAE41-B3B4-49A0-8B60-48AFE6A3BF6A}" type="CELLRANGE">
+                    <a:fld id="{3FDD22F4-96DF-46AA-952A-DF76E59ED2F8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1802,7 +1802,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{17EB1791-0AFB-4F8E-85C3-A99607CE31E8}" type="CELLRANGE">
+                    <a:fld id="{A52B121E-9159-4982-9647-0942D07B3899}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1836,7 +1836,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{06DD9118-998E-4E52-AB95-D0055FBE08EC}" type="CELLRANGE">
+                    <a:fld id="{2624BAB9-7C9B-4FBC-9056-C102B10C5DDF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1870,7 +1870,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DA365F32-443F-439C-901F-3B90D01E05B2}" type="CELLRANGE">
+                    <a:fld id="{B8B5422B-2D93-423D-9867-EB82D3CBF778}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1904,7 +1904,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DFA2C739-7E00-4569-89D9-038696E30C18}" type="CELLRANGE">
+                    <a:fld id="{D8CBCB61-7218-4D91-A489-8DEE2CE41D55}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1938,7 +1938,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{20AE6C04-3B74-4C31-B475-10F35842C548}" type="CELLRANGE">
+                    <a:fld id="{F7D9304E-C4F3-4A97-B6A5-2B2B43971E89}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -1972,7 +1972,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DB60A831-B2E9-49A9-A145-8DFDC78443C6}" type="CELLRANGE">
+                    <a:fld id="{DA6110C7-A225-450B-A1E4-C2918E098025}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2006,7 +2006,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A21B692F-5060-4905-9EDE-A5C9939029F8}" type="CELLRANGE">
+                    <a:fld id="{555EF69E-B3DB-4A57-B781-4388A6DD9EB5}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2040,7 +2040,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{38271A87-C9BC-4937-9DCF-AD30AD97B06E}" type="CELLRANGE">
+                    <a:fld id="{4D8E20A6-80F5-468E-ACE6-C0EE17F1ACC8}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2074,7 +2074,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F3C3B93A-6402-415F-B72B-8310DFC3EC1E}" type="CELLRANGE">
+                    <a:fld id="{986C2EC4-68A8-42BA-9BAE-50FB2B0B170F}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2108,7 +2108,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{489F7521-4FF1-4ECC-B830-A2E7D3D3C9AD}" type="CELLRANGE">
+                    <a:fld id="{F6615A68-6195-4EE3-86E4-4358475A5391}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2142,7 +2142,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7090F557-D22A-4F3B-B8DD-D81313A742D7}" type="CELLRANGE">
+                    <a:fld id="{C666CE85-C0D2-43B9-9348-97C45473B117}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -2236,7 +2236,7 @@
                   <c:v>⚠️ Validations &amp; Business Rules (31)</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>RAI Management (8)</c:v>
+                  <c:v>RAI Management (0)</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>SRT Review (9)</c:v>
@@ -2287,7 +2287,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -2331,6 +2331,9 @@
                 <c15:f>Dashboard_Data!$H$2:$H$15</c15:f>
                 <c15:dlblRangeCache>
                   <c:ptCount val="14"/>
+                  <c:pt idx="2">
+                    <c:v>Not Automated</c:v>
+                  </c:pt>
                   <c:pt idx="8">
                     <c:v>Not Automated</c:v>
                   </c:pt>
@@ -3540,21 +3543,13 @@
       <c r="A4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="10">
-        <v>8</v>
-      </c>
-      <c r="C4" s="10">
-        <v>8</v>
-      </c>
-      <c r="D4" s="10">
-        <v>0</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="7" t="str">
         <f t="shared" ref="F4:F16" si="0">IF(B4=0,"",C4/B4)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="G4" s="7">
         <f t="shared" ref="G4:G14" si="1">IFERROR(D4/B4,0)</f>
@@ -3885,11 +3880,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B3:B16)</f>
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C17" s="14">
         <f>SUM(C3:C15)</f>
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D17" s="14">
         <f>SUM(D3:D15)</f>
@@ -3901,11 +3896,11 @@
       </c>
       <c r="F17" s="15">
         <f t="shared" ref="F17" si="4">IFERROR(C17/B17,0)</f>
-        <v>0.96938775510204078</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="G17" s="15">
         <f t="shared" ref="G17" si="5">IFERROR(D17/B17,0)</f>
-        <v>3.0612244897959183E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="H17" s="15">
         <f t="shared" si="3"/>
@@ -4005,7 +4000,7 @@
       </c>
       <c r="H4" s="17">
         <f>TestCoverage!B17</f>
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -4022,7 +4017,7 @@
       </c>
       <c r="H5" s="17">
         <f>TestCoverage!C17</f>
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -4073,7 +4068,7 @@
       </c>
       <c r="H8" s="16">
         <f>IFERROR(H5/H4,"")</f>
-        <v>0.96938775510204078</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -4183,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="20">
-        <f>C2 + D2</f>
+        <f t="shared" ref="E2:E15" si="0">C2 + D2</f>
         <v>1</v>
       </c>
       <c r="F2" s="19">
@@ -4191,19 +4186,19 @@
         <v>1</v>
       </c>
       <c r="G2" s="18">
-        <f>IF($F2=0,1,0)</f>
+        <f t="shared" ref="G2:G15" si="1">IF($F2=0,1,0)</f>
         <v>0</v>
       </c>
       <c r="H2" s="19" t="str">
-        <f>IF(G2=100%,"Not Automated","")</f>
+        <f t="shared" ref="H2:H15" si="2">IF(G2=100%,"Not Automated","")</f>
         <v/>
       </c>
       <c r="I2" s="19" t="str">
-        <f>IF(AND(C2&gt;0,F2&gt;0),"⚠️ "&amp;A2,A2)</f>
+        <f t="shared" ref="I2:I15" si="3">IF(AND(C2&gt;0,F2&gt;0),"⚠️ "&amp;A2,A2)</f>
         <v>⚠️ Accessibility (Section 508 Compliance) (1)</v>
       </c>
       <c r="J2" s="19" t="str">
-        <f>IF(D2=100%,"Blocked","")</f>
+        <f t="shared" ref="J2:J15" si="4">IF(D2=100%,"Blocked","")</f>
         <v/>
       </c>
     </row>
@@ -4225,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="20">
-        <f>C3 + D3</f>
+        <f t="shared" si="0"/>
         <v>6.4516129032258063E-2</v>
       </c>
       <c r="F3" s="19">
@@ -4233,30 +4228,30 @@
         <v>31</v>
       </c>
       <c r="G3" s="18">
-        <f>IF($F3=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H3" s="19" t="str">
-        <f>IF(G3=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I3" s="19" t="str">
-        <f>IF(AND(C3&gt;0,F3&gt;0),"⚠️ "&amp;A3,A3)</f>
+        <f t="shared" si="3"/>
         <v>⚠️ Validations &amp; Business Rules (31)</v>
       </c>
       <c r="J3" s="19" t="str">
-        <f>IF(D3=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="str">
         <f>TestCoverage!A4 &amp; " (" &amp; IFERROR(TestCoverage!B4+0,0) &amp; ")"</f>
-        <v>RAI Management (8)</v>
-      </c>
-      <c r="B4" s="20">
+        <v>RAI Management (0)</v>
+      </c>
+      <c r="B4" s="20" t="str">
         <f>TestCoverage!F4</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="C4" s="20">
         <f>TestCoverage!G4</f>
@@ -4267,27 +4262,27 @@
         <v>0</v>
       </c>
       <c r="E4" s="20">
-        <f>C4 + D4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F4" s="19">
         <f>TestCoverage!B4</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G4" s="18">
-        <f>IF($F4=0,1,0)</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="H4" s="19" t="str">
-        <f>IF(G4=100%,"Not Automated","")</f>
-        <v/>
+        <f t="shared" si="2"/>
+        <v>Not Automated</v>
       </c>
       <c r="I4" s="19" t="str">
-        <f>IF(AND(C4&gt;0,F4&gt;0),"⚠️ "&amp;A4,A4)</f>
-        <v>RAI Management (8)</v>
+        <f t="shared" si="3"/>
+        <v>RAI Management (0)</v>
       </c>
       <c r="J4" s="19" t="str">
-        <f>IF(D4=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4309,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="20">
-        <f>C5 + D5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F5" s="19">
@@ -4317,19 +4312,19 @@
         <v>9</v>
       </c>
       <c r="G5" s="18">
-        <f>IF($F5=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H5" s="19" t="str">
-        <f>IF(G5=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I5" s="19" t="str">
-        <f>IF(AND(C5&gt;0,F5&gt;0),"⚠️ "&amp;A5,A5)</f>
+        <f t="shared" si="3"/>
         <v>SRT Review (9)</v>
       </c>
       <c r="J5" s="19" t="str">
-        <f>IF(D5=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4351,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="20">
-        <f>C6 + D6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F6" s="19">
@@ -4359,19 +4354,19 @@
         <v>7</v>
       </c>
       <c r="G6" s="18">
-        <f>IF($F6=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H6" s="19" t="str">
-        <f>IF(G6=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I6" s="19" t="str">
-        <f>IF(AND(C6&gt;0,F6&gt;0),"⚠️ "&amp;A6,A6)</f>
+        <f t="shared" si="3"/>
         <v>Workflow &amp; Status Transitions (7)</v>
       </c>
       <c r="J6" s="19" t="str">
-        <f>IF(D6=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4393,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="20">
-        <f>C7 + D7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F7" s="19">
@@ -4401,19 +4396,19 @@
         <v>17</v>
       </c>
       <c r="G7" s="18">
-        <f>IF($F7=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H7" s="19" t="str">
-        <f>IF(G7=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I7" s="19" t="str">
-        <f>IF(AND(C7&gt;0,F7&gt;0),"⚠️ "&amp;A7,A7)</f>
+        <f t="shared" si="3"/>
         <v>Record Lifecycle Management (17)</v>
       </c>
       <c r="J7" s="19" t="str">
-        <f>IF(D7=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4435,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="20">
-        <f>C8 + D8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F8" s="19">
@@ -4443,19 +4438,19 @@
         <v>7</v>
       </c>
       <c r="G8" s="18">
-        <f>IF($F8=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H8" s="19" t="str">
-        <f>IF(G8=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I8" s="19" t="str">
-        <f>IF(AND(C8&gt;0,F8&gt;0),"⚠️ "&amp;A8,A8)</f>
+        <f t="shared" si="3"/>
         <v>User Access &amp; Permissions (7)</v>
       </c>
       <c r="J8" s="19" t="str">
-        <f>IF(D8=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4477,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="20">
-        <f>C9 + D9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F9" s="19">
@@ -4485,19 +4480,19 @@
         <v>8</v>
       </c>
       <c r="G9" s="18">
-        <f>IF($F9=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H9" s="19" t="str">
-        <f>IF(G9=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I9" s="19" t="str">
-        <f>IF(AND(C9&gt;0,F9&gt;0),"⚠️ "&amp;A9,A9)</f>
+        <f t="shared" si="3"/>
         <v>Assignment &amp; Routing (8)</v>
       </c>
       <c r="J9" s="19" t="str">
-        <f>IF(D9=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4519,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="20">
-        <f>C10 + D10</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F10" s="19">
@@ -4527,19 +4522,19 @@
         <v>0</v>
       </c>
       <c r="G10" s="18">
-        <f>IF($F10=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H10" s="19" t="str">
-        <f>IF(G10=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I10" s="19" t="str">
-        <f>IF(AND(C10&gt;0,F10&gt;0),"⚠️ "&amp;A10,A10)</f>
+        <f t="shared" si="3"/>
         <v>API End To End (0)</v>
       </c>
       <c r="J10" s="19" t="str">
-        <f>IF(D10=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4561,7 +4556,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="20">
-        <f>C11 + D11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F11" s="19">
@@ -4569,19 +4564,19 @@
         <v>0</v>
       </c>
       <c r="G11" s="18">
-        <f>IF($F11=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H11" s="19" t="str">
-        <f>IF(G11=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I11" s="19" t="str">
-        <f>IF(AND(C11&gt;0,F11&gt;0),"⚠️ "&amp;A11,A11)</f>
+        <f t="shared" si="3"/>
         <v>Search &amp; Filters (0)</v>
       </c>
       <c r="J11" s="19" t="str">
-        <f>IF(D11=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4603,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="20">
-        <f>C12 + D12</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F12" s="19">
@@ -4611,19 +4606,19 @@
         <v>0</v>
       </c>
       <c r="G12" s="18">
-        <f>IF($F12=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H12" s="19" t="str">
-        <f>IF(G12=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I12" s="19" t="str">
-        <f>IF(AND(C12&gt;0,F12&gt;0),"⚠️ "&amp;A12,A12)</f>
+        <f t="shared" si="3"/>
         <v>Reporting &amp; Data Export (0)</v>
       </c>
       <c r="J12" s="19" t="str">
-        <f>IF(D12=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4645,7 +4640,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="20">
-        <f>C13 + D13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F13" s="19">
@@ -4653,19 +4648,19 @@
         <v>0</v>
       </c>
       <c r="G13" s="18">
-        <f>IF($F13=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H13" s="19" t="str">
-        <f>IF(G13=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I13" s="19" t="str">
-        <f>IF(AND(C13&gt;0,F13&gt;0),"⚠️ "&amp;A13,A13)</f>
+        <f t="shared" si="3"/>
         <v>Email Notifications &amp; Alerts (0)</v>
       </c>
       <c r="J13" s="19" t="str">
-        <f>IF(D13=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4687,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="20">
-        <f>C14 + D14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F14" s="19">
@@ -4695,19 +4690,19 @@
         <v>10</v>
       </c>
       <c r="G14" s="18">
-        <f>IF($F14=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H14" s="19" t="str">
-        <f>IF(G14=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I14" s="19" t="str">
-        <f>IF(AND(C14&gt;0,F14&gt;0),"⚠️ "&amp;A14,A14)</f>
+        <f t="shared" si="3"/>
         <v>Timeline &amp; SLA Management (10)</v>
       </c>
       <c r="J14" s="19" t="str">
-        <f>IF(D14=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -4729,7 +4724,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="20">
-        <f>C15 + D15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F15" s="19">
@@ -4737,34 +4732,34 @@
         <v>0</v>
       </c>
       <c r="G15" s="18">
-        <f>IF($F15=0,1,0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H15" s="19" t="str">
-        <f>IF(G15=100%,"Not Automated","")</f>
+        <f t="shared" si="2"/>
         <v>Not Automated</v>
       </c>
       <c r="I15" s="19" t="str">
-        <f>IF(AND(C15&gt;0,F15&gt;0),"⚠️ "&amp;A15,A15)</f>
+        <f t="shared" si="3"/>
         <v>Document Management (0)</v>
       </c>
       <c r="J15" s="19" t="str">
-        <f>IF(D15=100%,"Blocked","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:10" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="str">
         <f>TestCoverage!A17 &amp; " (" &amp; TestCoverage!B17 &amp; ")"</f>
-        <v>TOTAL (98)</v>
+        <v>TOTAL (90)</v>
       </c>
       <c r="B16" s="20">
         <f>TestCoverage!F17</f>
-        <v>0.96938775510204078</v>
+        <v>0.96666666666666667</v>
       </c>
       <c r="C16" s="20">
         <f>TestCoverage!G17</f>
-        <v>3.0612244897959183E-2</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="D16" s="20">
         <f>TestCoverage!H17</f>
@@ -4773,11 +4768,11 @@
       <c r="E16" s="20"/>
       <c r="F16" s="19">
         <f>TestCoverage!B17</f>
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G16" s="18">
         <f>COUNTIF(F2:F14,0)/COUNTA(A2:A14)</f>
-        <v>0.30769230769230771</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
